--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY444"/>
+  <dimension ref="A1:AY445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49215,59 +49215,48 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>60535102</v>
+        <v>135359375</v>
       </c>
       <c r="B438" t="n">
-        <v>57947</v>
+        <v>56908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E438" t="n">
-        <v>102977</v>
+        <v>100041</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K438" t="inlineStr"/>
-      <c r="L438" t="inlineStr"/>
-      <c r="M438" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Laurenti, 1768</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr"/>
       <c r="P438" t="inlineStr">
         <is>
-          <t>Roffe Ornö, Ornöboda, Srm</t>
+          <t>Brännkrok, Srm</t>
         </is>
       </c>
       <c r="Q438" t="n">
-        <v>699391</v>
+        <v>699406</v>
       </c>
       <c r="R438" t="n">
-        <v>6557647</v>
+        <v>6557753</v>
       </c>
       <c r="S438" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T438" t="inlineStr">
         <is>
@@ -49291,22 +49280,22 @@
       </c>
       <c r="Y438" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z438" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA438" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB438" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD438" t="b">
@@ -49319,24 +49308,14 @@
         <v>0</v>
       </c>
       <c r="AT438" t="inlineStr"/>
-      <c r="AW438" t="inlineStr">
-        <is>
-          <t>Henning Edgren</t>
-        </is>
-      </c>
-      <c r="AX438" t="inlineStr">
-        <is>
-          <t>Henning Edgren</t>
-        </is>
-      </c>
       <c r="AY438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>67887174</v>
+        <v>60535102</v>
       </c>
       <c r="B439" t="n">
-        <v>89079</v>
+        <v>57947</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -49344,36 +49323,45 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>239209</v>
+        <v>102977</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I439" t="inlineStr"/>
-      <c r="J439" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P439" t="inlineStr">
         <is>
-          <t>Ornöboda, Ornö, Srm</t>
+          <t>Roffe Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q439" t="n">
-        <v>699293</v>
+        <v>699391</v>
       </c>
       <c r="R439" t="n">
-        <v>6557679</v>
+        <v>6557647</v>
       </c>
       <c r="S439" t="n">
         <v>50</v>
@@ -49400,17 +49388,22 @@
       </c>
       <c r="Y439" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="Z439" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA439" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
-        </is>
-      </c>
-      <c r="AC439" t="inlineStr">
-        <is>
-          <t>Exkursion med Stockholms Svampvänner.</t>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="AB439" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD439" t="b">
@@ -49419,29 +49412,28 @@
       <c r="AE439" t="b">
         <v>0</v>
       </c>
-      <c r="AF439" t="inlineStr"/>
       <c r="AG439" t="b">
         <v>0</v>
       </c>
       <c r="AT439" t="inlineStr"/>
       <c r="AW439" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX439" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AY439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>67977656</v>
+        <v>67887174</v>
       </c>
       <c r="B440" t="n">
-        <v>75300</v>
+        <v>89079</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -49449,21 +49441,21 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>6428</v>
+        <v>239209</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I440" t="inlineStr"/>
@@ -49471,17 +49463,17 @@
       <c r="K440" t="inlineStr"/>
       <c r="P440" t="inlineStr">
         <is>
-          <t>Ornöboda, Srm</t>
+          <t>Ornöboda, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q440" t="n">
-        <v>699295</v>
+        <v>699293</v>
       </c>
       <c r="R440" t="n">
-        <v>6558099</v>
+        <v>6557679</v>
       </c>
       <c r="S440" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T440" t="inlineStr">
         <is>
@@ -49515,7 +49507,7 @@
       </c>
       <c r="AC440" t="inlineStr">
         <is>
-          <t>På gammal al.</t>
+          <t>Exkursion med Stockholms Svampvänner.</t>
         </is>
       </c>
       <c r="AD440" t="b">
@@ -49524,28 +49516,29 @@
       <c r="AE440" t="b">
         <v>0</v>
       </c>
+      <c r="AF440" t="inlineStr"/>
       <c r="AG440" t="b">
         <v>0</v>
       </c>
       <c r="AT440" t="inlineStr"/>
       <c r="AW440" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AX440" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AY440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>61833368</v>
+        <v>67977656</v>
       </c>
       <c r="B441" t="n">
-        <v>4775</v>
+        <v>75300</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -49553,37 +49546,39 @@
         </is>
       </c>
       <c r="E441" t="n">
-        <v>100299</v>
+        <v>6428</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="inlineStr"/>
       <c r="P441" t="inlineStr">
         <is>
-          <t>Ornöboda, Svinåker 3:40, Srm</t>
+          <t>Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q441" t="n">
-        <v>699294</v>
+        <v>699295</v>
       </c>
       <c r="R441" t="n">
-        <v>6558102</v>
+        <v>6558099</v>
       </c>
       <c r="S441" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="T441" t="inlineStr">
         <is>
@@ -49607,17 +49602,17 @@
       </c>
       <c r="Y441" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA441" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AC441" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>På gammal al.</t>
         </is>
       </c>
       <c r="AD441" t="b">
@@ -49632,26 +49627,22 @@
       <c r="AT441" t="inlineStr"/>
       <c r="AW441" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX441" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY441" t="inlineStr">
-        <is>
-          <t>Skötselplan Ornöboda Svinåker 3:15</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>60530282</v>
+        <v>61833368</v>
       </c>
       <c r="B442" t="n">
-        <v>58439</v>
+        <v>4775</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -49659,48 +49650,37 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>103018</v>
+        <v>100299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I442" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K442" t="inlineStr"/>
-      <c r="L442" t="inlineStr"/>
-      <c r="M442" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr"/>
       <c r="P442" t="inlineStr">
         <is>
-          <t>Ornö, Ornöboda, Srm</t>
+          <t>Ornöboda, Svinåker 3:40, Srm</t>
         </is>
       </c>
       <c r="Q442" t="n">
-        <v>699373</v>
+        <v>699294</v>
       </c>
       <c r="R442" t="n">
-        <v>6557918</v>
+        <v>6558102</v>
       </c>
       <c r="S442" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="T442" t="inlineStr">
         <is>
@@ -49724,22 +49704,17 @@
       </c>
       <c r="Y442" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="Z442" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AA442" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="AB442" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AC442" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AD442" t="b">
@@ -49754,72 +49729,75 @@
       <c r="AT442" t="inlineStr"/>
       <c r="AW442" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AX442" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
-        </is>
-      </c>
-      <c r="AY442" t="inlineStr"/>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY442" t="inlineStr">
+        <is>
+          <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>118137472</v>
+        <v>60530282</v>
       </c>
       <c r="B443" t="n">
-        <v>57572</v>
+        <v>58439</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E443" t="n">
-        <v>205660</v>
+        <v>103018</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr"/>
       <c r="M443" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N443" t="inlineStr"/>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="P443" t="inlineStr">
         <is>
-          <t>Inloppet till Toren, Ornö, Srm</t>
+          <t>Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q443" t="n">
-        <v>699420</v>
+        <v>699373</v>
       </c>
       <c r="R443" t="n">
-        <v>6557948</v>
+        <v>6557918</v>
       </c>
       <c r="S443" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T443" t="inlineStr">
         <is>
@@ -49843,12 +49821,22 @@
       </c>
       <c r="Y443" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="Z443" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA443" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="AB443" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD443" t="b">
@@ -49863,60 +49851,72 @@
       <c r="AT443" t="inlineStr"/>
       <c r="AW443" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX443" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AY443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>61833348</v>
+        <v>118137472</v>
       </c>
       <c r="B444" t="n">
-        <v>4781</v>
+        <v>57572</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>102306</v>
+        <v>205660</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I444" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr"/>
       <c r="P444" t="inlineStr">
         <is>
-          <t>Ornöboda, Svinåker 3:20, Srm</t>
+          <t>Inloppet till Toren, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q444" t="n">
-        <v>699344</v>
+        <v>699420</v>
       </c>
       <c r="R444" t="n">
-        <v>6558123</v>
+        <v>6557948</v>
       </c>
       <c r="S444" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -49940,17 +49940,12 @@
       </c>
       <c r="Y444" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA444" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AC444" t="inlineStr">
-        <is>
-          <t>Märkta av svs för fällning. Inväxta i ek.</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD444" t="b">
@@ -49965,15 +49960,117 @@
       <c r="AT444" t="inlineStr"/>
       <c r="AW444" t="inlineStr">
         <is>
+          <t>Per Åsberg</t>
+        </is>
+      </c>
+      <c r="AX444" t="inlineStr">
+        <is>
+          <t>Per Åsberg</t>
+        </is>
+      </c>
+      <c r="AY444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>61833348</v>
+      </c>
+      <c r="B445" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr"/>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>Ornöboda, Svinåker 3:20, Srm</t>
+        </is>
+      </c>
+      <c r="Q445" t="n">
+        <v>699344</v>
+      </c>
+      <c r="R445" t="n">
+        <v>6558123</v>
+      </c>
+      <c r="S445" t="n">
+        <v>15</v>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AC445" t="inlineStr">
+        <is>
+          <t>Märkta av svs för fällning. Inväxta i ek.</t>
+        </is>
+      </c>
+      <c r="AD445" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE445" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG445" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT445" t="inlineStr"/>
+      <c r="AW445" t="inlineStr">
+        <is>
           <t>Anna Koffman</t>
         </is>
       </c>
-      <c r="AX444" t="inlineStr">
+      <c r="AX445" t="inlineStr">
         <is>
           <t>Anna Koffman</t>
         </is>
       </c>
-      <c r="AY444" t="inlineStr">
+      <c r="AY445" t="inlineStr">
         <is>
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -49308,6 +49308,16 @@
         <v>0</v>
       </c>
       <c r="AT438" t="inlineStr"/>
+      <c r="AW438" t="inlineStr">
+        <is>
+          <t>Mira Karlin Bittár</t>
+        </is>
+      </c>
+      <c r="AX438" t="inlineStr">
+        <is>
+          <t>Mira Karlin Bittár</t>
+        </is>
+      </c>
       <c r="AY438" t="inlineStr"/>
     </row>
     <row r="439">

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY451"/>
+  <dimension ref="A1:AZ451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319853</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540903</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540902</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,6 +1167,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319339</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,6 +1283,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319726</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319795</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,6 +1521,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122321257</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122310585</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1732,6 +1777,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540883</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1868,6 +1918,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540897</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2004,6 +2059,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540898</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2136,6 +2196,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540882</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2243,6 +2308,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540879</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2370,6 +2440,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540881</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2480,6 +2555,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095066</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2590,6 +2670,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095067</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2700,6 +2785,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095071</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2810,6 +2900,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095072</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2920,6 +3015,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095073</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3030,6 +3130,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095074</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3140,6 +3245,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095075</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3247,6 +3357,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122324705</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3362,6 +3477,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74370745</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3489,6 +3609,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75243710</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3605,6 +3730,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122309800</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3721,6 +3851,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122311493</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3853,6 +3988,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540878</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3960,6 +4100,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122540896</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4066,6 +4211,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019812</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4172,6 +4322,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019840</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4278,6 +4433,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019848</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4395,6 +4555,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122586258</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4501,6 +4666,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019824</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4607,6 +4777,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019820</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4713,6 +4888,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019821</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4825,6 +5005,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122586261</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4935,6 +5120,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095054</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5045,6 +5235,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095060</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5155,6 +5350,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095061</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5265,6 +5465,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095062</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5375,6 +5580,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095065</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5485,6 +5695,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095068</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5595,6 +5810,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095069</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5705,6 +5925,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095070</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5812,6 +6037,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095401</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5918,6 +6148,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019826</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6024,6 +6259,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019825</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6130,6 +6370,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019827</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6236,6 +6481,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019811</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6342,6 +6592,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019836</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6444,6 +6699,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095413</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6554,6 +6814,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095056</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6664,6 +6929,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095057</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6774,6 +7044,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095058</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6884,6 +7159,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095059</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7006,6 +7286,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713486</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7143,6 +7428,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713485</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7250,6 +7540,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713494</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7357,6 +7652,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713490</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7464,6 +7764,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713495</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7571,6 +7876,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713491</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7681,6 +7991,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095052</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7791,6 +8106,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094971</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7899,6 +8219,11 @@
       <c r="AY65" t="inlineStr">
         <is>
           <t>Svampinventering Sthlm Län 2018</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095051</t>
         </is>
       </c>
     </row>
@@ -8012,6 +8337,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713686</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8144,6 +8474,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713496</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8255,6 +8590,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133216797</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8371,6 +8711,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14861059</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8478,6 +8823,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713493</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8585,6 +8935,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713497</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8701,6 +9056,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3917302</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8808,6 +9168,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713489</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8924,6 +9289,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117013</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9040,6 +9410,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/237541</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9151,6 +9526,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/186073</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9266,6 +9646,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095053</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9377,6 +9762,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1104985</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9493,6 +9883,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/730305</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9604,6 +9999,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1618039</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9714,6 +10114,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094968</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9824,6 +10229,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094969</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9934,6 +10344,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094970</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10044,6 +10459,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095038</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10160,6 +10580,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1651361</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10276,6 +10701,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2003842</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10391,6 +10821,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90630560</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10506,6 +10941,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126286280</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10617,6 +11057,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2294060</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10724,6 +11169,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303829</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10831,6 +11281,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303824</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10951,6 +11406,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095036</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11066,6 +11526,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094967</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11181,6 +11646,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095035</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11291,6 +11761,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095031</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11401,6 +11876,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095032</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11511,6 +11991,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095033</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11621,6 +12106,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095034</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11731,6 +12221,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095037</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11841,6 +12336,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095039</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11955,6 +12455,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126286241</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12076,6 +12581,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117353417</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12191,6 +12701,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095029</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12301,6 +12816,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095028</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12416,6 +12936,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095030</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12526,6 +13051,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095025</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12636,6 +13166,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095026</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12746,6 +13281,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095027</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12861,6 +13401,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74371634</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12983,6 +13528,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75243708</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13103,6 +13653,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74370969</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13218,6 +13773,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74370762</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13339,6 +13899,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75243701</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13450,6 +14015,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74370606</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13565,6 +14135,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74370522</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13675,6 +14250,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74371081</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13793,6 +14373,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126288241</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13907,6 +14492,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135509586</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14017,6 +14607,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094981</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14127,6 +14722,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094982</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14242,6 +14842,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094983</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14349,6 +14954,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96242672</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14464,6 +15074,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094972</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14570,6 +15185,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094987</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14680,6 +15300,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094984</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14787,6 +15412,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96285755</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14889,6 +15519,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56623457</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14999,6 +15634,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094996</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15114,6 +15754,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095047</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15227,6 +15872,11 @@
       <c r="AY130" t="inlineStr">
         <is>
           <t>Svampinventering Sthlm Län 2018</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095049</t>
         </is>
       </c>
     </row>
@@ -15334,6 +15984,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290048</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15440,6 +16095,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095048</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15548,6 +16208,11 @@
       <c r="AY133" t="inlineStr">
         <is>
           <t>Svampinventering Sthlm Län 2018</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094997</t>
         </is>
       </c>
     </row>
@@ -15661,6 +16326,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290054</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15762,6 +16432,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13108043</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15884,6 +16559,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13984422</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15989,6 +16669,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290041</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16099,6 +16784,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094985</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16209,6 +16899,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095001</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16319,6 +17014,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095012</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16441,6 +17141,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303852</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16541,6 +17246,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290309</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16647,6 +17357,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412019</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16754,6 +17469,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303818</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16869,6 +17589,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095046</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16975,6 +17700,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019709</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17085,6 +17815,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095002</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17195,6 +17930,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095043</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17318,6 +18058,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095044</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17441,6 +18186,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095045</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17551,6 +18301,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095050</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17662,6 +18417,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1764082</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17768,6 +18528,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019710</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17874,6 +18639,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019708</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17990,6 +18760,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75243713</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18096,6 +18871,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412018</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18206,6 +18986,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74371082</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18333,6 +19118,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303816</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18440,6 +19230,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303850</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18547,6 +19342,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303849</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18662,6 +19462,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095003</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18777,6 +19582,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095014</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18888,6 +19698,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/277348</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19008,6 +19823,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095011</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19115,6 +19935,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119304120</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19231,6 +20056,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/643169</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19347,6 +20177,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/681158</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19463,6 +20298,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/859160</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19579,6 +20419,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/677116</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19684,6 +20529,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290323</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19800,6 +20650,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1618040</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19910,6 +20765,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095013</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20020,6 +20880,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095016</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20147,6 +21012,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303814</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20262,6 +21132,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095015</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20378,6 +21253,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2003843</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20510,6 +21390,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303813</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20621,6 +21506,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2209154</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20732,6 +21622,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2369157</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20843,6 +21738,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4972278</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20954,6 +21854,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5251448</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21069,6 +21974,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095019</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21179,6 +22089,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095018</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21289,6 +22204,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095020</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21399,6 +22319,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095021</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21509,6 +22434,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095022</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21619,6 +22549,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095024</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21735,6 +22670,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72104706</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21851,6 +22791,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75243690</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21952,6 +22897,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702914</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22072,6 +23022,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125602881</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22189,6 +23144,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125603143</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22299,6 +23259,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121750940</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22410,6 +23375,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125601821</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22529,6 +23499,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126288317</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22648,6 +23623,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127031401</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22763,6 +23743,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125601459</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22878,6 +23863,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121750876</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22989,6 +23979,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122308276</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23104,6 +24099,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125601457</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23215,6 +24215,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121750915</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23326,6 +24331,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126741110</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23423,6 +24433,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118082575</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23532,6 +24547,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134924065</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23647,6 +24667,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094979</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23761,6 +24786,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409023</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23871,6 +24901,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408943</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23981,6 +25016,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094980</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -24089,6 +25129,11 @@
       <c r="AY209" t="inlineStr">
         <is>
           <t>Svampinventering Sthlm Län 2018</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094990</t>
         </is>
       </c>
     </row>
@@ -24201,6 +25246,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408945</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24307,6 +25357,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2209158</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24426,6 +25481,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126287888</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24532,6 +25592,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4972569</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24642,6 +25707,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094989</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24752,6 +25822,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094974</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24862,6 +25937,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094993</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24977,6 +26057,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094973</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -25085,6 +26170,11 @@
       <c r="AY218" t="inlineStr">
         <is>
           <t>Svampinventering Sthlm Län 2018</t>
+        </is>
+      </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094975</t>
         </is>
       </c>
     </row>
@@ -25187,6 +26277,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290170</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25294,6 +26389,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303836</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25404,6 +26504,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095000</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25514,6 +26619,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094995</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25622,6 +26732,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290220</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25722,6 +26837,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290243</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25830,6 +26950,11 @@
       <c r="AY225" t="inlineStr">
         <is>
           <t>Svampinventering Sthlm Län 2018</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75094998</t>
         </is>
       </c>
     </row>
@@ -25943,6 +27068,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290236</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26075,6 +27205,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303843</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26182,6 +27317,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303842</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26287,6 +27427,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290294</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26392,6 +27537,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290278</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26492,6 +27642,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290216</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26597,6 +27752,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290254</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26702,6 +27862,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290257</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26810,6 +27975,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290298</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26921,6 +28091,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290269</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -27032,6 +28207,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290301</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -27138,6 +28318,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77991240</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27242,6 +28427,11 @@
       <c r="AY238" t="inlineStr">
         <is>
           <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1029182</t>
         </is>
       </c>
     </row>
@@ -27349,6 +28539,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290329</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27455,6 +28650,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107486055</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27561,6 +28761,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/676768</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27667,6 +28872,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107486054</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27773,6 +28983,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107486062</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27873,6 +29088,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290345</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27988,6 +29208,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095010</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -28088,6 +29313,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290337</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28188,6 +29418,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290344</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28294,6 +29529,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107486059</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28409,6 +29649,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095009</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28515,6 +29760,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107486053</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28642,6 +29892,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303894</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28779,6 +30034,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303892</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28891,6 +30151,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303889</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28998,6 +30263,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303855</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -29098,6 +30368,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290354</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -29198,6 +30473,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290475</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -29299,6 +30579,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107486050</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -29406,6 +30691,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303891</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -29505,6 +30795,11 @@
       <c r="AY259" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107486052</t>
         </is>
       </c>
     </row>
@@ -29607,6 +30902,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290467</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29708,6 +31008,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107486061</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29821,6 +31126,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290334</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29920,6 +31230,11 @@
       <c r="AY263" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107486060</t>
         </is>
       </c>
     </row>
@@ -30022,6 +31337,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290479</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -30123,6 +31443,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107486063</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -30230,6 +31555,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303890</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -30330,6 +31660,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290434</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -30431,6 +31766,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107486058</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -30538,6 +31878,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119303893</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -30638,6 +31983,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290487</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -30753,6 +32103,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095004</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30868,6 +32223,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095007</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30976,6 +32336,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290555</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -31086,6 +32451,11 @@
           <t>Svampinventering Sthlm Län 2018</t>
         </is>
       </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095005</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -31194,6 +32564,11 @@
       <c r="AY275" t="inlineStr">
         <is>
           <t>Svampinventering Sthlm Län 2018</t>
+        </is>
+      </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75095006</t>
         </is>
       </c>
     </row>
@@ -31301,6 +32676,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290540</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -31401,6 +32781,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290521</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -31514,6 +32899,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290576</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -31627,6 +33017,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290593</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31732,6 +33127,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290510</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31853,6 +33253,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811935</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31979,6 +33384,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119813698</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -32100,6 +33510,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119813522</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -32215,6 +33630,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126288439</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -32329,6 +33749,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125604126</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -32441,6 +33866,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125604421</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -32555,6 +33985,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125559476</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -32666,6 +34101,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125542218</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -32779,6 +34219,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290109</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -32879,6 +34324,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290163</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -32994,6 +34444,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125559670</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -33102,6 +34557,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290173</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -33207,6 +34667,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290208</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -33307,6 +34772,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290177</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -33421,6 +34891,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122317692</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -33536,6 +35011,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126287057</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -33650,6 +35130,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128431475</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -33765,6 +35250,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126286990</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -33881,6 +35371,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126286988</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -33992,6 +35487,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290058</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -34103,6 +35603,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290188</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -34214,6 +35719,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290202</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -34330,6 +35840,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126275902</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -34430,6 +35945,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66290200</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -34535,6 +36055,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977740</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -34640,6 +36165,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977769</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -34745,6 +36275,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67885765</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -34850,6 +36385,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977755</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -34961,6 +36501,11 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833344</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -35082,6 +36627,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119812963</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -35196,6 +36746,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125549918</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -35310,6 +36865,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125549968</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -35424,6 +36984,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125541490</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -35545,6 +37110,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125564788</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -35660,6 +37230,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125542792</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -35771,6 +37346,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126287769</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -35885,6 +37465,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125542848</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -35999,6 +37584,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543050</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -36109,6 +37699,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543236</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -36223,6 +37818,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125544301</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -36337,6 +37937,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125544797</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -36456,6 +38061,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125545115</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -36575,6 +38185,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125545144</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -36689,6 +38304,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125545168</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -36803,6 +38423,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125545173</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -36917,6 +38542,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562521</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -37028,6 +38658,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128428913</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -37149,6 +38784,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125560278</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -37265,6 +38905,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562641</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -37386,6 +39031,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562871</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -37507,6 +39157,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125563979</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -37623,6 +39278,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126274856</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -37740,6 +39400,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126275690</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -37856,6 +39521,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125544404</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -37976,6 +39646,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125545005</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -38096,6 +39771,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125545089</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -38216,6 +39896,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562787</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -38332,6 +40017,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562714</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -38447,6 +40137,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125544570</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -38562,6 +40257,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125544973</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -38677,6 +40377,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125561081</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -38793,6 +40498,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543656</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -38914,6 +40624,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125561863</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -39030,6 +40745,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562025</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -39146,6 +40866,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125561666</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -39262,6 +40987,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125599235</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -39373,6 +41103,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128429467</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -39484,6 +41219,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128430527</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -39603,6 +41343,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126277663</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -39714,6 +41459,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128429714</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -39824,6 +41574,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135490968</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -39939,6 +41694,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128430681</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -40054,6 +41814,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128431305</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -40165,6 +41930,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126277662</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -40275,6 +42045,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128430378</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -40385,6 +42160,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128430719</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -40496,6 +42276,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491929</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -40607,6 +42392,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128430442</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -40721,6 +42511,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128430843</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -40831,6 +42626,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126276922</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -40946,6 +42746,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126277769</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -41062,6 +42867,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126275450</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -41186,6 +42996,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491918</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -41302,6 +43117,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126276189</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -41418,6 +43238,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126276416</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -41534,6 +43359,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126277302</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -41650,6 +43480,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126277831</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -41766,6 +43601,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126277229</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -41882,6 +43722,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126287696</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -41998,6 +43843,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491919</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -42110,6 +43960,11 @@
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126341339</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -42225,6 +44080,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128430975</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -42325,6 +44185,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128884792</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -42435,6 +44300,11 @@
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128431155</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -42536,6 +44406,11 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833364</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -42641,6 +44516,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67885581</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -42746,6 +44626,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977773</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -42851,6 +44736,11 @@
         </is>
       </c>
       <c r="AY378" t="inlineStr"/>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67883039</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -42956,6 +44846,11 @@
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977612</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -43061,6 +44956,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67888004</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -43166,6 +45066,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977589</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -43271,6 +45176,11 @@
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67886172</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -43376,6 +45286,11 @@
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67882641</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -43481,6 +45396,11 @@
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977581</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -43586,6 +45506,11 @@
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67882629</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -43692,6 +45617,11 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833357</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -43798,6 +45728,11 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833359</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -43902,6 +45837,11 @@
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67885579</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -44007,6 +45947,11 @@
         </is>
       </c>
       <c r="AY389" t="inlineStr"/>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67884398</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -44113,6 +46058,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019805</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -44219,6 +46169,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019808</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -44324,6 +46279,11 @@
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67884309</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -44440,6 +46400,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/164040</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -44545,6 +46510,11 @@
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977711</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -44651,6 +46621,11 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833345</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -44767,6 +46742,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/681136</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -44883,6 +46863,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1027748</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -44999,6 +46984,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/676320</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -45103,6 +47093,11 @@
       <c r="AY399" t="inlineStr">
         <is>
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833350</t>
         </is>
       </c>
     </row>
@@ -45210,6 +47205,11 @@
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67884408</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -45316,6 +47316,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019799</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -45417,6 +47422,11 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833351</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -45523,6 +47533,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019800</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -45629,6 +47644,11 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833358</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -45735,6 +47755,11 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833360</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -45841,6 +47866,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019801</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -45942,6 +47972,11 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833365</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -46041,6 +48076,11 @@
       <c r="AY408" t="inlineStr">
         <is>
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833363</t>
         </is>
       </c>
     </row>
@@ -46154,6 +48194,11 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833361</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -46270,6 +48315,11 @@
         </is>
       </c>
       <c r="AY410" t="inlineStr"/>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79288912</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -46381,6 +48431,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2209144</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -46490,6 +48545,11 @@
       <c r="AY412" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4971347</t>
         </is>
       </c>
     </row>
@@ -46597,6 +48657,11 @@
         </is>
       </c>
       <c r="AY413" t="inlineStr"/>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977686</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -46702,6 +48767,11 @@
         </is>
       </c>
       <c r="AY414" t="inlineStr"/>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977664</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -46807,6 +48877,11 @@
         </is>
       </c>
       <c r="AY415" t="inlineStr"/>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977672</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -46912,6 +48987,11 @@
         </is>
       </c>
       <c r="AY416" t="inlineStr"/>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977677</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -47018,6 +49098,11 @@
         </is>
       </c>
       <c r="AY417" t="inlineStr"/>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977663</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -47116,6 +49201,11 @@
         </is>
       </c>
       <c r="AY418" t="inlineStr"/>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96407986</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -47237,6 +49327,11 @@
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119812988</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -47352,6 +49447,11 @@
         </is>
       </c>
       <c r="AY420" t="inlineStr"/>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134560725</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -47475,6 +49575,11 @@
         </is>
       </c>
       <c r="AY421" t="inlineStr"/>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128405730</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -47585,6 +49690,11 @@
         </is>
       </c>
       <c r="AY422" t="inlineStr"/>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124228864</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -47703,6 +49813,11 @@
         </is>
       </c>
       <c r="AY423" t="inlineStr"/>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128419433</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -47827,6 +49942,11 @@
         </is>
       </c>
       <c r="AY424" t="inlineStr"/>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127055232</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -47946,6 +50066,11 @@
         </is>
       </c>
       <c r="AY425" t="inlineStr"/>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125594772</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -48062,6 +50187,11 @@
         </is>
       </c>
       <c r="AY426" t="inlineStr"/>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125604856</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -48177,6 +50307,11 @@
         </is>
       </c>
       <c r="AY427" t="inlineStr"/>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126748727</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -48293,6 +50428,11 @@
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126748605</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -48413,6 +50553,11 @@
         </is>
       </c>
       <c r="AY429" t="inlineStr"/>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126748712</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -48533,6 +50678,11 @@
         </is>
       </c>
       <c r="AY430" t="inlineStr"/>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126748606</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -48639,6 +50789,11 @@
         </is>
       </c>
       <c r="AY431" t="inlineStr"/>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126748448</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -48750,6 +50905,11 @@
         </is>
       </c>
       <c r="AY432" t="inlineStr"/>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491340</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -48859,6 +51019,11 @@
         </is>
       </c>
       <c r="AY433" t="inlineStr"/>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118137486</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -48964,6 +51129,11 @@
         </is>
       </c>
       <c r="AY434" t="inlineStr"/>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67883426</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -49069,6 +51239,11 @@
         </is>
       </c>
       <c r="AY435" t="inlineStr"/>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67881075</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -49174,6 +51349,11 @@
         </is>
       </c>
       <c r="AY436" t="inlineStr"/>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67886202</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -49275,6 +51455,11 @@
         </is>
       </c>
       <c r="AY437" t="inlineStr"/>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67883313</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -49376,6 +51561,11 @@
         </is>
       </c>
       <c r="AY438" t="inlineStr"/>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977554</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -49477,6 +51667,11 @@
         </is>
       </c>
       <c r="AY439" t="inlineStr"/>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67881006</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -49582,6 +51777,11 @@
         </is>
       </c>
       <c r="AY440" t="inlineStr"/>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67883352</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -49688,6 +51888,11 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833367</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -49793,6 +51998,11 @@
         </is>
       </c>
       <c r="AY442" t="inlineStr"/>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67881085</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -49898,6 +52108,11 @@
         </is>
       </c>
       <c r="AY443" t="inlineStr"/>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977514</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -50005,6 +52220,11 @@
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359375</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -50123,6 +52343,11 @@
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60535102</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -50228,6 +52453,11 @@
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67887174</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -50332,6 +52562,11 @@
         </is>
       </c>
       <c r="AY447" t="inlineStr"/>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977656</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -50438,6 +52673,11 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833368</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -50556,6 +52796,11 @@
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60530282</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -50665,6 +52910,11 @@
         </is>
       </c>
       <c r="AY450" t="inlineStr"/>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118137472</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -50771,8 +53021,465 @@
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61833348</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -14384,7 +14384,7 @@
         <v>135509586</v>
       </c>
       <c r="B118" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>134924065</v>
       </c>
       <c r="B204" t="n">
-        <v>91993</v>
+        <v>92035</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>135490968</v>
       </c>
       <c r="B351" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>135491929</v>
       </c>
       <c r="B357" t="n">
-        <v>92031</v>
+        <v>92073</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>135491918</v>
       </c>
       <c r="B363" t="n">
-        <v>9422</v>
+        <v>9423</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>135491919</v>
       </c>
       <c r="B370" t="n">
-        <v>30293</v>
+        <v>30296</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>135491340</v>
       </c>
       <c r="B432" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>135359375</v>
       </c>
       <c r="B444" t="n">
-        <v>56908</v>
+        <v>56913</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ451"/>
+  <dimension ref="A1:AZ450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14384,7 +14384,7 @@
         <v>135509586</v>
       </c>
       <c r="B118" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>135490968</v>
       </c>
       <c r="B351" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>135491929</v>
       </c>
       <c r="B357" t="n">
-        <v>92073</v>
+        <v>92100</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>135491340</v>
       </c>
       <c r="B432" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -52116,48 +52116,59 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>135359375</v>
+        <v>60535102</v>
       </c>
       <c r="B444" t="n">
-        <v>56913</v>
+        <v>57947</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>100041</v>
+        <v>102977</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Coronella austriaca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Laurenti, 1768</t>
-        </is>
-      </c>
-      <c r="I444" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P444" t="inlineStr">
         <is>
-          <t>Brännkrok, Srm</t>
+          <t>Roffe Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q444" t="n">
-        <v>699406</v>
+        <v>699391</v>
       </c>
       <c r="R444" t="n">
-        <v>6557753</v>
+        <v>6557647</v>
       </c>
       <c r="S444" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -52181,22 +52192,22 @@
       </c>
       <c r="Y444" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="Z444" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA444" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="AB444" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD444" t="b">
@@ -52211,27 +52222,27 @@
       <c r="AT444" t="inlineStr"/>
       <c r="AW444" t="inlineStr">
         <is>
-          <t>Mira Karlin Bittár</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX444" t="inlineStr">
         <is>
-          <t>Mira Karlin Bittár</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
       <c r="AZ444" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135359375</t>
+          <t>https://artportalen.se/Sighting/60535102</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>60535102</v>
+        <v>67887174</v>
       </c>
       <c r="B445" t="n">
-        <v>57947</v>
+        <v>89079</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52239,45 +52250,36 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>102977</v>
+        <v>239209</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I445" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr"/>
-      <c r="L445" t="inlineStr"/>
-      <c r="M445" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P445" t="inlineStr">
         <is>
-          <t>Roffe Ornö, Ornöboda, Srm</t>
+          <t>Ornöboda, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>699391</v>
+        <v>699293</v>
       </c>
       <c r="R445" t="n">
-        <v>6557647</v>
+        <v>6557679</v>
       </c>
       <c r="S445" t="n">
         <v>50</v>
@@ -52304,22 +52306,17 @@
       </c>
       <c r="Y445" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
-        </is>
-      </c>
-      <c r="Z445" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA445" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
-        </is>
-      </c>
-      <c r="AB445" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2017-09-30</t>
+        </is>
+      </c>
+      <c r="AC445" t="inlineStr">
+        <is>
+          <t>Exkursion med Stockholms Svampvänner.</t>
         </is>
       </c>
       <c r="AD445" t="b">
@@ -52328,33 +52325,34 @@
       <c r="AE445" t="b">
         <v>0</v>
       </c>
+      <c r="AF445" t="inlineStr"/>
       <c r="AG445" t="b">
         <v>0</v>
       </c>
       <c r="AT445" t="inlineStr"/>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
       <c r="AZ445" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60535102</t>
+          <t>https://artportalen.se/Sighting/67887174</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>67887174</v>
+        <v>67977656</v>
       </c>
       <c r="B446" t="n">
-        <v>89079</v>
+        <v>75300</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52362,21 +52360,21 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>239209</v>
+        <v>6428</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I446" t="inlineStr"/>
@@ -52384,17 +52382,17 @@
       <c r="K446" t="inlineStr"/>
       <c r="P446" t="inlineStr">
         <is>
-          <t>Ornöboda, Ornö, Srm</t>
+          <t>Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>699293</v>
+        <v>699295</v>
       </c>
       <c r="R446" t="n">
-        <v>6557679</v>
+        <v>6558099</v>
       </c>
       <c r="S446" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T446" t="inlineStr">
         <is>
@@ -52428,7 +52426,7 @@
       </c>
       <c r="AC446" t="inlineStr">
         <is>
-          <t>Exkursion med Stockholms Svampvänner.</t>
+          <t>På gammal al.</t>
         </is>
       </c>
       <c r="AD446" t="b">
@@ -52437,34 +52435,33 @@
       <c r="AE446" t="b">
         <v>0</v>
       </c>
-      <c r="AF446" t="inlineStr"/>
       <c r="AG446" t="b">
         <v>0</v>
       </c>
       <c r="AT446" t="inlineStr"/>
       <c r="AW446" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX446" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
       <c r="AZ446" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67887174</t>
+          <t>https://artportalen.se/Sighting/67977656</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>67977656</v>
+        <v>61833368</v>
       </c>
       <c r="B447" t="n">
-        <v>75300</v>
+        <v>4775</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52472,39 +52469,37 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>6428</v>
+        <v>100299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I447" t="inlineStr"/>
-      <c r="J447" t="inlineStr"/>
-      <c r="K447" t="inlineStr"/>
       <c r="P447" t="inlineStr">
         <is>
-          <t>Ornöboda, Srm</t>
+          <t>Ornöboda, Svinåker 3:40, Srm</t>
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>699295</v>
+        <v>699294</v>
       </c>
       <c r="R447" t="n">
-        <v>6558099</v>
+        <v>6558102</v>
       </c>
       <c r="S447" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="T447" t="inlineStr">
         <is>
@@ -52528,17 +52523,17 @@
       </c>
       <c r="Y447" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AA447" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AC447" t="inlineStr">
         <is>
-          <t>På gammal al.</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AD447" t="b">
@@ -52553,27 +52548,31 @@
       <c r="AT447" t="inlineStr"/>
       <c r="AW447" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AX447" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY447" t="inlineStr"/>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY447" t="inlineStr">
+        <is>
+          <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
       <c r="AZ447" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67977656</t>
+          <t>https://artportalen.se/Sighting/61833368</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>61833368</v>
+        <v>60530282</v>
       </c>
       <c r="B448" t="n">
-        <v>4775</v>
+        <v>58439</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52581,37 +52580,48 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>100299</v>
+        <v>103018</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I448" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="P448" t="inlineStr">
         <is>
-          <t>Ornöboda, Svinåker 3:40, Srm</t>
+          <t>Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q448" t="n">
-        <v>699294</v>
+        <v>699373</v>
       </c>
       <c r="R448" t="n">
-        <v>6558102</v>
+        <v>6557918</v>
       </c>
       <c r="S448" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -52635,17 +52645,22 @@
       </c>
       <c r="Y448" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="Z448" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA448" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AC448" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="AB448" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD448" t="b">
@@ -52660,80 +52675,77 @@
       <c r="AT448" t="inlineStr"/>
       <c r="AW448" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX448" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY448" t="inlineStr">
-        <is>
-          <t>Skötselplan Ornöboda Svinåker 3:15</t>
-        </is>
-      </c>
+          <t>Henning Edgren</t>
+        </is>
+      </c>
+      <c r="AY448" t="inlineStr"/>
       <c r="AZ448" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61833368</t>
+          <t>https://artportalen.se/Sighting/60530282</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>60530282</v>
+        <v>118137472</v>
       </c>
       <c r="B449" t="n">
-        <v>58439</v>
+        <v>57572</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>103018</v>
+        <v>205660</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr"/>
       <c r="P449" t="inlineStr">
         <is>
-          <t>Ornö, Ornöboda, Srm</t>
+          <t>Inloppet till Toren, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q449" t="n">
-        <v>699373</v>
+        <v>699420</v>
       </c>
       <c r="R449" t="n">
-        <v>6557918</v>
+        <v>6557948</v>
       </c>
       <c r="S449" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
@@ -52757,22 +52769,12 @@
       </c>
       <c r="Y449" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="Z449" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA449" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="AB449" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD449" t="b">
@@ -52787,77 +52789,65 @@
       <c r="AT449" t="inlineStr"/>
       <c r="AW449" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Per Åsberg</t>
         </is>
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Per Åsberg</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
       <c r="AZ449" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60530282</t>
+          <t>https://artportalen.se/Sighting/118137472</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>118137472</v>
+        <v>61833348</v>
       </c>
       <c r="B450" t="n">
-        <v>57572</v>
+        <v>4781</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>205660</v>
+        <v>102306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K450" t="inlineStr"/>
-      <c r="L450" t="inlineStr"/>
-      <c r="M450" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N450" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr"/>
       <c r="P450" t="inlineStr">
         <is>
-          <t>Inloppet till Toren, Ornö, Srm</t>
+          <t>Ornöboda, Svinåker 3:20, Srm</t>
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>699420</v>
+        <v>699344</v>
       </c>
       <c r="R450" t="n">
-        <v>6557948</v>
+        <v>6558123</v>
       </c>
       <c r="S450" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T450" t="inlineStr">
         <is>
@@ -52881,12 +52871,17 @@
       </c>
       <c r="Y450" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AA450" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AC450" t="inlineStr">
+        <is>
+          <t>Märkta av svs för fällning. Inväxta i ek.</t>
         </is>
       </c>
       <c r="AD450" t="b">
@@ -52901,127 +52896,20 @@
       <c r="AT450" t="inlineStr"/>
       <c r="AW450" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AX450" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
-        </is>
-      </c>
-      <c r="AY450" t="inlineStr"/>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY450" t="inlineStr">
+        <is>
+          <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
       <c r="AZ450" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/118137472</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="n">
-        <v>61833348</v>
-      </c>
-      <c r="B451" t="n">
-        <v>4781</v>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E451" t="n">
-        <v>102306</v>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>Granbarkgnagare</t>
-        </is>
-      </c>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>Microbregma emarginatum</t>
-        </is>
-      </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I451" t="inlineStr"/>
-      <c r="P451" t="inlineStr">
-        <is>
-          <t>Ornöboda, Svinåker 3:20, Srm</t>
-        </is>
-      </c>
-      <c r="Q451" t="n">
-        <v>699344</v>
-      </c>
-      <c r="R451" t="n">
-        <v>6558123</v>
-      </c>
-      <c r="S451" t="n">
-        <v>15</v>
-      </c>
-      <c r="T451" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U451" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V451" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W451" t="inlineStr">
-        <is>
-          <t>Ornö</t>
-        </is>
-      </c>
-      <c r="Y451" t="inlineStr">
-        <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AA451" t="inlineStr">
-        <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AC451" t="inlineStr">
-        <is>
-          <t>Märkta av svs för fällning. Inväxta i ek.</t>
-        </is>
-      </c>
-      <c r="AD451" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE451" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG451" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT451" t="inlineStr"/>
-      <c r="AW451" t="inlineStr">
-        <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AX451" t="inlineStr">
-        <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY451" t="inlineStr">
-        <is>
-          <t>Skötselplan Ornöboda Svinåker 3:15</t>
-        </is>
-      </c>
-      <c r="AZ451" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/61833348</t>
         </is>
@@ -53478,7 +53366,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ450"/>
+  <dimension ref="A1:AZ451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52116,59 +52116,48 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>60535102</v>
+        <v>135359375</v>
       </c>
       <c r="B444" t="n">
-        <v>57947</v>
+        <v>56913</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>102977</v>
+        <v>100041</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I444" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K444" t="inlineStr"/>
-      <c r="L444" t="inlineStr"/>
-      <c r="M444" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Laurenti, 1768</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr"/>
       <c r="P444" t="inlineStr">
         <is>
-          <t>Roffe Ornö, Ornöboda, Srm</t>
+          <t>Brännkrok, Srm</t>
         </is>
       </c>
       <c r="Q444" t="n">
-        <v>699391</v>
+        <v>699406</v>
       </c>
       <c r="R444" t="n">
-        <v>6557647</v>
+        <v>6557753</v>
       </c>
       <c r="S444" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -52192,22 +52181,22 @@
       </c>
       <c r="Y444" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z444" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA444" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB444" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD444" t="b">
@@ -52222,27 +52211,27 @@
       <c r="AT444" t="inlineStr"/>
       <c r="AW444" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Mira Karlin Bittár</t>
         </is>
       </c>
       <c r="AX444" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Mira Karlin Bittár</t>
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
       <c r="AZ444" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60535102</t>
+          <t>https://artportalen.se/Sighting/135359375</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>67887174</v>
+        <v>60535102</v>
       </c>
       <c r="B445" t="n">
-        <v>89079</v>
+        <v>57947</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52250,36 +52239,45 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>239209</v>
+        <v>102977</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P445" t="inlineStr">
         <is>
-          <t>Ornöboda, Ornö, Srm</t>
+          <t>Roffe Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>699293</v>
+        <v>699391</v>
       </c>
       <c r="R445" t="n">
-        <v>6557679</v>
+        <v>6557647</v>
       </c>
       <c r="S445" t="n">
         <v>50</v>
@@ -52306,17 +52304,22 @@
       </c>
       <c r="Y445" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA445" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
-        </is>
-      </c>
-      <c r="AC445" t="inlineStr">
-        <is>
-          <t>Exkursion med Stockholms Svampvänner.</t>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="AB445" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD445" t="b">
@@ -52325,34 +52328,33 @@
       <c r="AE445" t="b">
         <v>0</v>
       </c>
-      <c r="AF445" t="inlineStr"/>
       <c r="AG445" t="b">
         <v>0</v>
       </c>
       <c r="AT445" t="inlineStr"/>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
       <c r="AZ445" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67887174</t>
+          <t>https://artportalen.se/Sighting/60535102</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>67977656</v>
+        <v>67887174</v>
       </c>
       <c r="B446" t="n">
-        <v>75300</v>
+        <v>89079</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52360,21 +52362,21 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6428</v>
+        <v>239209</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I446" t="inlineStr"/>
@@ -52382,17 +52384,17 @@
       <c r="K446" t="inlineStr"/>
       <c r="P446" t="inlineStr">
         <is>
-          <t>Ornöboda, Srm</t>
+          <t>Ornöboda, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>699295</v>
+        <v>699293</v>
       </c>
       <c r="R446" t="n">
-        <v>6558099</v>
+        <v>6557679</v>
       </c>
       <c r="S446" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T446" t="inlineStr">
         <is>
@@ -52426,7 +52428,7 @@
       </c>
       <c r="AC446" t="inlineStr">
         <is>
-          <t>På gammal al.</t>
+          <t>Exkursion med Stockholms Svampvänner.</t>
         </is>
       </c>
       <c r="AD446" t="b">
@@ -52435,33 +52437,34 @@
       <c r="AE446" t="b">
         <v>0</v>
       </c>
+      <c r="AF446" t="inlineStr"/>
       <c r="AG446" t="b">
         <v>0</v>
       </c>
       <c r="AT446" t="inlineStr"/>
       <c r="AW446" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AX446" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
       <c r="AZ446" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67977656</t>
+          <t>https://artportalen.se/Sighting/67887174</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>61833368</v>
+        <v>67977656</v>
       </c>
       <c r="B447" t="n">
-        <v>4775</v>
+        <v>75300</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52469,37 +52472,39 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>100299</v>
+        <v>6428</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr"/>
       <c r="P447" t="inlineStr">
         <is>
-          <t>Ornöboda, Svinåker 3:40, Srm</t>
+          <t>Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>699294</v>
+        <v>699295</v>
       </c>
       <c r="R447" t="n">
-        <v>6558102</v>
+        <v>6558099</v>
       </c>
       <c r="S447" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="T447" t="inlineStr">
         <is>
@@ -52523,17 +52528,17 @@
       </c>
       <c r="Y447" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA447" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AC447" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>På gammal al.</t>
         </is>
       </c>
       <c r="AD447" t="b">
@@ -52548,31 +52553,27 @@
       <c r="AT447" t="inlineStr"/>
       <c r="AW447" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX447" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY447" t="inlineStr">
-        <is>
-          <t>Skötselplan Ornöboda Svinåker 3:15</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY447" t="inlineStr"/>
       <c r="AZ447" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61833368</t>
+          <t>https://artportalen.se/Sighting/67977656</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>60530282</v>
+        <v>61833368</v>
       </c>
       <c r="B448" t="n">
-        <v>58439</v>
+        <v>4775</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52580,48 +52581,37 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>103018</v>
+        <v>100299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I448" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K448" t="inlineStr"/>
-      <c r="L448" t="inlineStr"/>
-      <c r="M448" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr"/>
       <c r="P448" t="inlineStr">
         <is>
-          <t>Ornö, Ornöboda, Srm</t>
+          <t>Ornöboda, Svinåker 3:40, Srm</t>
         </is>
       </c>
       <c r="Q448" t="n">
-        <v>699373</v>
+        <v>699294</v>
       </c>
       <c r="R448" t="n">
-        <v>6557918</v>
+        <v>6558102</v>
       </c>
       <c r="S448" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -52645,22 +52635,17 @@
       </c>
       <c r="Y448" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="Z448" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AA448" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="AB448" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AC448" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AD448" t="b">
@@ -52675,77 +52660,80 @@
       <c r="AT448" t="inlineStr"/>
       <c r="AW448" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AX448" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
-        </is>
-      </c>
-      <c r="AY448" t="inlineStr"/>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY448" t="inlineStr">
+        <is>
+          <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
       <c r="AZ448" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60530282</t>
+          <t>https://artportalen.se/Sighting/61833368</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>118137472</v>
+        <v>60530282</v>
       </c>
       <c r="B449" t="n">
-        <v>57572</v>
+        <v>58439</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>205660</v>
+        <v>103018</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N449" t="inlineStr"/>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="P449" t="inlineStr">
         <is>
-          <t>Inloppet till Toren, Ornö, Srm</t>
+          <t>Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q449" t="n">
-        <v>699420</v>
+        <v>699373</v>
       </c>
       <c r="R449" t="n">
-        <v>6557948</v>
+        <v>6557918</v>
       </c>
       <c r="S449" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
@@ -52769,12 +52757,22 @@
       </c>
       <c r="Y449" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="Z449" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA449" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="AB449" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD449" t="b">
@@ -52789,65 +52787,77 @@
       <c r="AT449" t="inlineStr"/>
       <c r="AW449" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
       <c r="AZ449" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118137472</t>
+          <t>https://artportalen.se/Sighting/60530282</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>61833348</v>
+        <v>118137472</v>
       </c>
       <c r="B450" t="n">
-        <v>4781</v>
+        <v>57572</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>102306</v>
+        <v>205660</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I450" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr"/>
       <c r="P450" t="inlineStr">
         <is>
-          <t>Ornöboda, Svinåker 3:20, Srm</t>
+          <t>Inloppet till Toren, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>699344</v>
+        <v>699420</v>
       </c>
       <c r="R450" t="n">
-        <v>6558123</v>
+        <v>6557948</v>
       </c>
       <c r="S450" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T450" t="inlineStr">
         <is>
@@ -52871,17 +52881,12 @@
       </c>
       <c r="Y450" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA450" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AC450" t="inlineStr">
-        <is>
-          <t>Märkta av svs för fällning. Inväxta i ek.</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD450" t="b">
@@ -52896,20 +52901,127 @@
       <c r="AT450" t="inlineStr"/>
       <c r="AW450" t="inlineStr">
         <is>
+          <t>Per Åsberg</t>
+        </is>
+      </c>
+      <c r="AX450" t="inlineStr">
+        <is>
+          <t>Per Åsberg</t>
+        </is>
+      </c>
+      <c r="AY450" t="inlineStr"/>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118137472</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>61833348</v>
+      </c>
+      <c r="B451" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr"/>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>Ornöboda, Svinåker 3:20, Srm</t>
+        </is>
+      </c>
+      <c r="Q451" t="n">
+        <v>699344</v>
+      </c>
+      <c r="R451" t="n">
+        <v>6558123</v>
+      </c>
+      <c r="S451" t="n">
+        <v>15</v>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W451" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y451" t="inlineStr">
+        <is>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AA451" t="inlineStr">
+        <is>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AC451" t="inlineStr">
+        <is>
+          <t>Märkta av svs för fällning. Inväxta i ek.</t>
+        </is>
+      </c>
+      <c r="AD451" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE451" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG451" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT451" t="inlineStr"/>
+      <c r="AW451" t="inlineStr">
+        <is>
           <t>Anna Koffman</t>
         </is>
       </c>
-      <c r="AX450" t="inlineStr">
+      <c r="AX451" t="inlineStr">
         <is>
           <t>Anna Koffman</t>
         </is>
       </c>
-      <c r="AY450" t="inlineStr">
+      <c r="AY451" t="inlineStr">
         <is>
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
-      <c r="AZ450" t="inlineStr">
+      <c r="AZ451" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/61833348</t>
         </is>
@@ -53366,6 +53478,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ451"/>
+  <dimension ref="A1:AZ450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52116,48 +52116,59 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>135359375</v>
+        <v>60535102</v>
       </c>
       <c r="B444" t="n">
-        <v>56913</v>
+        <v>57947</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>100041</v>
+        <v>102977</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Coronella austriaca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Laurenti, 1768</t>
-        </is>
-      </c>
-      <c r="I444" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P444" t="inlineStr">
         <is>
-          <t>Brännkrok, Srm</t>
+          <t>Roffe Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q444" t="n">
-        <v>699406</v>
+        <v>699391</v>
       </c>
       <c r="R444" t="n">
-        <v>6557753</v>
+        <v>6557647</v>
       </c>
       <c r="S444" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -52181,22 +52192,22 @@
       </c>
       <c r="Y444" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="Z444" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA444" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="AB444" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD444" t="b">
@@ -52211,27 +52222,27 @@
       <c r="AT444" t="inlineStr"/>
       <c r="AW444" t="inlineStr">
         <is>
-          <t>Mira Karlin Bittár</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX444" t="inlineStr">
         <is>
-          <t>Mira Karlin Bittár</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
       <c r="AZ444" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135359375</t>
+          <t>https://artportalen.se/Sighting/60535102</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>60535102</v>
+        <v>67887174</v>
       </c>
       <c r="B445" t="n">
-        <v>57947</v>
+        <v>89079</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52239,45 +52250,36 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>102977</v>
+        <v>239209</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I445" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr"/>
-      <c r="L445" t="inlineStr"/>
-      <c r="M445" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P445" t="inlineStr">
         <is>
-          <t>Roffe Ornö, Ornöboda, Srm</t>
+          <t>Ornöboda, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>699391</v>
+        <v>699293</v>
       </c>
       <c r="R445" t="n">
-        <v>6557647</v>
+        <v>6557679</v>
       </c>
       <c r="S445" t="n">
         <v>50</v>
@@ -52304,22 +52306,17 @@
       </c>
       <c r="Y445" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
-        </is>
-      </c>
-      <c r="Z445" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA445" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
-        </is>
-      </c>
-      <c r="AB445" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2017-09-30</t>
+        </is>
+      </c>
+      <c r="AC445" t="inlineStr">
+        <is>
+          <t>Exkursion med Stockholms Svampvänner.</t>
         </is>
       </c>
       <c r="AD445" t="b">
@@ -52328,33 +52325,34 @@
       <c r="AE445" t="b">
         <v>0</v>
       </c>
+      <c r="AF445" t="inlineStr"/>
       <c r="AG445" t="b">
         <v>0</v>
       </c>
       <c r="AT445" t="inlineStr"/>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
       <c r="AZ445" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60535102</t>
+          <t>https://artportalen.se/Sighting/67887174</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>67887174</v>
+        <v>67977656</v>
       </c>
       <c r="B446" t="n">
-        <v>89079</v>
+        <v>75300</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52362,21 +52360,21 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>239209</v>
+        <v>6428</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I446" t="inlineStr"/>
@@ -52384,17 +52382,17 @@
       <c r="K446" t="inlineStr"/>
       <c r="P446" t="inlineStr">
         <is>
-          <t>Ornöboda, Ornö, Srm</t>
+          <t>Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>699293</v>
+        <v>699295</v>
       </c>
       <c r="R446" t="n">
-        <v>6557679</v>
+        <v>6558099</v>
       </c>
       <c r="S446" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T446" t="inlineStr">
         <is>
@@ -52428,7 +52426,7 @@
       </c>
       <c r="AC446" t="inlineStr">
         <is>
-          <t>Exkursion med Stockholms Svampvänner.</t>
+          <t>På gammal al.</t>
         </is>
       </c>
       <c r="AD446" t="b">
@@ -52437,34 +52435,33 @@
       <c r="AE446" t="b">
         <v>0</v>
       </c>
-      <c r="AF446" t="inlineStr"/>
       <c r="AG446" t="b">
         <v>0</v>
       </c>
       <c r="AT446" t="inlineStr"/>
       <c r="AW446" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX446" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
       <c r="AZ446" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67887174</t>
+          <t>https://artportalen.se/Sighting/67977656</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>67977656</v>
+        <v>61833368</v>
       </c>
       <c r="B447" t="n">
-        <v>75300</v>
+        <v>4775</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52472,39 +52469,37 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>6428</v>
+        <v>100299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I447" t="inlineStr"/>
-      <c r="J447" t="inlineStr"/>
-      <c r="K447" t="inlineStr"/>
       <c r="P447" t="inlineStr">
         <is>
-          <t>Ornöboda, Srm</t>
+          <t>Ornöboda, Svinåker 3:40, Srm</t>
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>699295</v>
+        <v>699294</v>
       </c>
       <c r="R447" t="n">
-        <v>6558099</v>
+        <v>6558102</v>
       </c>
       <c r="S447" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="T447" t="inlineStr">
         <is>
@@ -52528,17 +52523,17 @@
       </c>
       <c r="Y447" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AA447" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AC447" t="inlineStr">
         <is>
-          <t>På gammal al.</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AD447" t="b">
@@ -52553,27 +52548,31 @@
       <c r="AT447" t="inlineStr"/>
       <c r="AW447" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AX447" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY447" t="inlineStr"/>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY447" t="inlineStr">
+        <is>
+          <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
       <c r="AZ447" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67977656</t>
+          <t>https://artportalen.se/Sighting/61833368</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>61833368</v>
+        <v>60530282</v>
       </c>
       <c r="B448" t="n">
-        <v>4775</v>
+        <v>58439</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52581,37 +52580,48 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>100299</v>
+        <v>103018</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I448" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="P448" t="inlineStr">
         <is>
-          <t>Ornöboda, Svinåker 3:40, Srm</t>
+          <t>Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q448" t="n">
-        <v>699294</v>
+        <v>699373</v>
       </c>
       <c r="R448" t="n">
-        <v>6558102</v>
+        <v>6557918</v>
       </c>
       <c r="S448" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -52635,17 +52645,22 @@
       </c>
       <c r="Y448" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="Z448" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA448" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AC448" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="AB448" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD448" t="b">
@@ -52660,80 +52675,77 @@
       <c r="AT448" t="inlineStr"/>
       <c r="AW448" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX448" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY448" t="inlineStr">
-        <is>
-          <t>Skötselplan Ornöboda Svinåker 3:15</t>
-        </is>
-      </c>
+          <t>Henning Edgren</t>
+        </is>
+      </c>
+      <c r="AY448" t="inlineStr"/>
       <c r="AZ448" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61833368</t>
+          <t>https://artportalen.se/Sighting/60530282</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>60530282</v>
+        <v>118137472</v>
       </c>
       <c r="B449" t="n">
-        <v>58439</v>
+        <v>57572</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>103018</v>
+        <v>205660</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr"/>
       <c r="P449" t="inlineStr">
         <is>
-          <t>Ornö, Ornöboda, Srm</t>
+          <t>Inloppet till Toren, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q449" t="n">
-        <v>699373</v>
+        <v>699420</v>
       </c>
       <c r="R449" t="n">
-        <v>6557918</v>
+        <v>6557948</v>
       </c>
       <c r="S449" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
@@ -52757,22 +52769,12 @@
       </c>
       <c r="Y449" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="Z449" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA449" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="AB449" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD449" t="b">
@@ -52787,77 +52789,65 @@
       <c r="AT449" t="inlineStr"/>
       <c r="AW449" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Per Åsberg</t>
         </is>
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Per Åsberg</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
       <c r="AZ449" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60530282</t>
+          <t>https://artportalen.se/Sighting/118137472</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>118137472</v>
+        <v>61833348</v>
       </c>
       <c r="B450" t="n">
-        <v>57572</v>
+        <v>4781</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>205660</v>
+        <v>102306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K450" t="inlineStr"/>
-      <c r="L450" t="inlineStr"/>
-      <c r="M450" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N450" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr"/>
       <c r="P450" t="inlineStr">
         <is>
-          <t>Inloppet till Toren, Ornö, Srm</t>
+          <t>Ornöboda, Svinåker 3:20, Srm</t>
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>699420</v>
+        <v>699344</v>
       </c>
       <c r="R450" t="n">
-        <v>6557948</v>
+        <v>6558123</v>
       </c>
       <c r="S450" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T450" t="inlineStr">
         <is>
@@ -52881,12 +52871,17 @@
       </c>
       <c r="Y450" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AA450" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AC450" t="inlineStr">
+        <is>
+          <t>Märkta av svs för fällning. Inväxta i ek.</t>
         </is>
       </c>
       <c r="AD450" t="b">
@@ -52901,127 +52896,20 @@
       <c r="AT450" t="inlineStr"/>
       <c r="AW450" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AX450" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
-        </is>
-      </c>
-      <c r="AY450" t="inlineStr"/>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY450" t="inlineStr">
+        <is>
+          <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
       <c r="AZ450" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/118137472</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="n">
-        <v>61833348</v>
-      </c>
-      <c r="B451" t="n">
-        <v>4781</v>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E451" t="n">
-        <v>102306</v>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>Granbarkgnagare</t>
-        </is>
-      </c>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>Microbregma emarginatum</t>
-        </is>
-      </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I451" t="inlineStr"/>
-      <c r="P451" t="inlineStr">
-        <is>
-          <t>Ornöboda, Svinåker 3:20, Srm</t>
-        </is>
-      </c>
-      <c r="Q451" t="n">
-        <v>699344</v>
-      </c>
-      <c r="R451" t="n">
-        <v>6558123</v>
-      </c>
-      <c r="S451" t="n">
-        <v>15</v>
-      </c>
-      <c r="T451" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U451" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V451" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W451" t="inlineStr">
-        <is>
-          <t>Ornö</t>
-        </is>
-      </c>
-      <c r="Y451" t="inlineStr">
-        <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AA451" t="inlineStr">
-        <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AC451" t="inlineStr">
-        <is>
-          <t>Märkta av svs för fällning. Inväxta i ek.</t>
-        </is>
-      </c>
-      <c r="AD451" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE451" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG451" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT451" t="inlineStr"/>
-      <c r="AW451" t="inlineStr">
-        <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AX451" t="inlineStr">
-        <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY451" t="inlineStr">
-        <is>
-          <t>Skötselplan Ornöboda Svinåker 3:15</t>
-        </is>
-      </c>
-      <c r="AZ451" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/61833348</t>
         </is>
@@ -53478,7 +53366,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -14384,7 +14384,7 @@
         <v>135509586</v>
       </c>
       <c r="B118" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>135490968</v>
       </c>
       <c r="B351" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>135491929</v>
       </c>
       <c r="B357" t="n">
-        <v>92105</v>
+        <v>92107</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>135491340</v>
       </c>
       <c r="B432" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -14384,7 +14384,7 @@
         <v>135509586</v>
       </c>
       <c r="B118" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>135490968</v>
       </c>
       <c r="B351" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>135491929</v>
       </c>
       <c r="B357" t="n">
-        <v>92107</v>
+        <v>92121</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>135491918</v>
       </c>
       <c r="B363" t="n">
-        <v>9423</v>
+        <v>9425</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>135491919</v>
       </c>
       <c r="B370" t="n">
-        <v>30296</v>
+        <v>30298</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>135491340</v>
       </c>
       <c r="B432" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>135359375</v>
       </c>
       <c r="B444" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ451"/>
+  <dimension ref="A1:AZ450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14384,7 +14384,7 @@
         <v>135509586</v>
       </c>
       <c r="B118" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>135490968</v>
       </c>
       <c r="B351" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>135491929</v>
       </c>
       <c r="B357" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>135491340</v>
       </c>
       <c r="B432" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -52116,48 +52116,59 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>135359375</v>
+        <v>60535102</v>
       </c>
       <c r="B444" t="n">
-        <v>56915</v>
+        <v>57947</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>100041</v>
+        <v>102977</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Coronella austriaca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Laurenti, 1768</t>
-        </is>
-      </c>
-      <c r="I444" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P444" t="inlineStr">
         <is>
-          <t>Brännkrok, Srm</t>
+          <t>Roffe Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q444" t="n">
-        <v>699406</v>
+        <v>699391</v>
       </c>
       <c r="R444" t="n">
-        <v>6557753</v>
+        <v>6557647</v>
       </c>
       <c r="S444" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -52181,22 +52192,22 @@
       </c>
       <c r="Y444" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="Z444" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA444" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="AB444" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD444" t="b">
@@ -52211,27 +52222,27 @@
       <c r="AT444" t="inlineStr"/>
       <c r="AW444" t="inlineStr">
         <is>
-          <t>Mira Karlin Bittár</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX444" t="inlineStr">
         <is>
-          <t>Mira Karlin Bittár</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
       <c r="AZ444" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135359375</t>
+          <t>https://artportalen.se/Sighting/60535102</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>60535102</v>
+        <v>67887174</v>
       </c>
       <c r="B445" t="n">
-        <v>57947</v>
+        <v>89079</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52239,45 +52250,36 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>102977</v>
+        <v>239209</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I445" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr"/>
-      <c r="L445" t="inlineStr"/>
-      <c r="M445" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P445" t="inlineStr">
         <is>
-          <t>Roffe Ornö, Ornöboda, Srm</t>
+          <t>Ornöboda, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>699391</v>
+        <v>699293</v>
       </c>
       <c r="R445" t="n">
-        <v>6557647</v>
+        <v>6557679</v>
       </c>
       <c r="S445" t="n">
         <v>50</v>
@@ -52304,22 +52306,17 @@
       </c>
       <c r="Y445" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
-        </is>
-      </c>
-      <c r="Z445" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA445" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
-        </is>
-      </c>
-      <c r="AB445" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2017-09-30</t>
+        </is>
+      </c>
+      <c r="AC445" t="inlineStr">
+        <is>
+          <t>Exkursion med Stockholms Svampvänner.</t>
         </is>
       </c>
       <c r="AD445" t="b">
@@ -52328,33 +52325,34 @@
       <c r="AE445" t="b">
         <v>0</v>
       </c>
+      <c r="AF445" t="inlineStr"/>
       <c r="AG445" t="b">
         <v>0</v>
       </c>
       <c r="AT445" t="inlineStr"/>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
       <c r="AZ445" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60535102</t>
+          <t>https://artportalen.se/Sighting/67887174</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>67887174</v>
+        <v>67977656</v>
       </c>
       <c r="B446" t="n">
-        <v>89079</v>
+        <v>75300</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52362,21 +52360,21 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>239209</v>
+        <v>6428</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I446" t="inlineStr"/>
@@ -52384,17 +52382,17 @@
       <c r="K446" t="inlineStr"/>
       <c r="P446" t="inlineStr">
         <is>
-          <t>Ornöboda, Ornö, Srm</t>
+          <t>Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>699293</v>
+        <v>699295</v>
       </c>
       <c r="R446" t="n">
-        <v>6557679</v>
+        <v>6558099</v>
       </c>
       <c r="S446" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T446" t="inlineStr">
         <is>
@@ -52428,7 +52426,7 @@
       </c>
       <c r="AC446" t="inlineStr">
         <is>
-          <t>Exkursion med Stockholms Svampvänner.</t>
+          <t>På gammal al.</t>
         </is>
       </c>
       <c r="AD446" t="b">
@@ -52437,34 +52435,33 @@
       <c r="AE446" t="b">
         <v>0</v>
       </c>
-      <c r="AF446" t="inlineStr"/>
       <c r="AG446" t="b">
         <v>0</v>
       </c>
       <c r="AT446" t="inlineStr"/>
       <c r="AW446" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX446" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
       <c r="AZ446" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67887174</t>
+          <t>https://artportalen.se/Sighting/67977656</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>67977656</v>
+        <v>61833368</v>
       </c>
       <c r="B447" t="n">
-        <v>75300</v>
+        <v>4775</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52472,39 +52469,37 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>6428</v>
+        <v>100299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I447" t="inlineStr"/>
-      <c r="J447" t="inlineStr"/>
-      <c r="K447" t="inlineStr"/>
       <c r="P447" t="inlineStr">
         <is>
-          <t>Ornöboda, Srm</t>
+          <t>Ornöboda, Svinåker 3:40, Srm</t>
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>699295</v>
+        <v>699294</v>
       </c>
       <c r="R447" t="n">
-        <v>6558099</v>
+        <v>6558102</v>
       </c>
       <c r="S447" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="T447" t="inlineStr">
         <is>
@@ -52528,17 +52523,17 @@
       </c>
       <c r="Y447" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AA447" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AC447" t="inlineStr">
         <is>
-          <t>På gammal al.</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AD447" t="b">
@@ -52553,27 +52548,31 @@
       <c r="AT447" t="inlineStr"/>
       <c r="AW447" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AX447" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY447" t="inlineStr"/>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY447" t="inlineStr">
+        <is>
+          <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
       <c r="AZ447" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67977656</t>
+          <t>https://artportalen.se/Sighting/61833368</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>61833368</v>
+        <v>60530282</v>
       </c>
       <c r="B448" t="n">
-        <v>4775</v>
+        <v>58439</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52581,37 +52580,48 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>100299</v>
+        <v>103018</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I448" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="P448" t="inlineStr">
         <is>
-          <t>Ornöboda, Svinåker 3:40, Srm</t>
+          <t>Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q448" t="n">
-        <v>699294</v>
+        <v>699373</v>
       </c>
       <c r="R448" t="n">
-        <v>6558102</v>
+        <v>6557918</v>
       </c>
       <c r="S448" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -52635,17 +52645,22 @@
       </c>
       <c r="Y448" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="Z448" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA448" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AC448" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="AB448" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD448" t="b">
@@ -52660,80 +52675,77 @@
       <c r="AT448" t="inlineStr"/>
       <c r="AW448" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX448" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY448" t="inlineStr">
-        <is>
-          <t>Skötselplan Ornöboda Svinåker 3:15</t>
-        </is>
-      </c>
+          <t>Henning Edgren</t>
+        </is>
+      </c>
+      <c r="AY448" t="inlineStr"/>
       <c r="AZ448" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61833368</t>
+          <t>https://artportalen.se/Sighting/60530282</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>60530282</v>
+        <v>118137472</v>
       </c>
       <c r="B449" t="n">
-        <v>58439</v>
+        <v>57572</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>103018</v>
+        <v>205660</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr"/>
       <c r="P449" t="inlineStr">
         <is>
-          <t>Ornö, Ornöboda, Srm</t>
+          <t>Inloppet till Toren, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q449" t="n">
-        <v>699373</v>
+        <v>699420</v>
       </c>
       <c r="R449" t="n">
-        <v>6557918</v>
+        <v>6557948</v>
       </c>
       <c r="S449" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
@@ -52757,22 +52769,12 @@
       </c>
       <c r="Y449" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="Z449" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA449" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="AB449" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD449" t="b">
@@ -52787,77 +52789,65 @@
       <c r="AT449" t="inlineStr"/>
       <c r="AW449" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Per Åsberg</t>
         </is>
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Per Åsberg</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
       <c r="AZ449" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60530282</t>
+          <t>https://artportalen.se/Sighting/118137472</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>118137472</v>
+        <v>61833348</v>
       </c>
       <c r="B450" t="n">
-        <v>57572</v>
+        <v>4781</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>205660</v>
+        <v>102306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K450" t="inlineStr"/>
-      <c r="L450" t="inlineStr"/>
-      <c r="M450" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N450" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr"/>
       <c r="P450" t="inlineStr">
         <is>
-          <t>Inloppet till Toren, Ornö, Srm</t>
+          <t>Ornöboda, Svinåker 3:20, Srm</t>
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>699420</v>
+        <v>699344</v>
       </c>
       <c r="R450" t="n">
-        <v>6557948</v>
+        <v>6558123</v>
       </c>
       <c r="S450" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T450" t="inlineStr">
         <is>
@@ -52881,12 +52871,17 @@
       </c>
       <c r="Y450" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AA450" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AC450" t="inlineStr">
+        <is>
+          <t>Märkta av svs för fällning. Inväxta i ek.</t>
         </is>
       </c>
       <c r="AD450" t="b">
@@ -52901,127 +52896,20 @@
       <c r="AT450" t="inlineStr"/>
       <c r="AW450" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AX450" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
-        </is>
-      </c>
-      <c r="AY450" t="inlineStr"/>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY450" t="inlineStr">
+        <is>
+          <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
       <c r="AZ450" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/118137472</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="n">
-        <v>61833348</v>
-      </c>
-      <c r="B451" t="n">
-        <v>4781</v>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E451" t="n">
-        <v>102306</v>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>Granbarkgnagare</t>
-        </is>
-      </c>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>Microbregma emarginatum</t>
-        </is>
-      </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I451" t="inlineStr"/>
-      <c r="P451" t="inlineStr">
-        <is>
-          <t>Ornöboda, Svinåker 3:20, Srm</t>
-        </is>
-      </c>
-      <c r="Q451" t="n">
-        <v>699344</v>
-      </c>
-      <c r="R451" t="n">
-        <v>6558123</v>
-      </c>
-      <c r="S451" t="n">
-        <v>15</v>
-      </c>
-      <c r="T451" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U451" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V451" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W451" t="inlineStr">
-        <is>
-          <t>Ornö</t>
-        </is>
-      </c>
-      <c r="Y451" t="inlineStr">
-        <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AA451" t="inlineStr">
-        <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AC451" t="inlineStr">
-        <is>
-          <t>Märkta av svs för fällning. Inväxta i ek.</t>
-        </is>
-      </c>
-      <c r="AD451" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE451" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG451" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT451" t="inlineStr"/>
-      <c r="AW451" t="inlineStr">
-        <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AX451" t="inlineStr">
-        <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY451" t="inlineStr">
-        <is>
-          <t>Skötselplan Ornöboda Svinåker 3:15</t>
-        </is>
-      </c>
-      <c r="AZ451" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/61833348</t>
         </is>
@@ -53478,7 +53366,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ450"/>
+  <dimension ref="A1:AZ451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52116,59 +52116,48 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>60535102</v>
+        <v>135359375</v>
       </c>
       <c r="B444" t="n">
-        <v>57947</v>
+        <v>56915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>102977</v>
+        <v>100041</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I444" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K444" t="inlineStr"/>
-      <c r="L444" t="inlineStr"/>
-      <c r="M444" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Laurenti, 1768</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr"/>
       <c r="P444" t="inlineStr">
         <is>
-          <t>Roffe Ornö, Ornöboda, Srm</t>
+          <t>Brännkrok, Srm</t>
         </is>
       </c>
       <c r="Q444" t="n">
-        <v>699391</v>
+        <v>699406</v>
       </c>
       <c r="R444" t="n">
-        <v>6557647</v>
+        <v>6557753</v>
       </c>
       <c r="S444" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -52192,22 +52181,22 @@
       </c>
       <c r="Y444" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z444" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA444" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB444" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD444" t="b">
@@ -52222,27 +52211,27 @@
       <c r="AT444" t="inlineStr"/>
       <c r="AW444" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Mira Karlin Bittár</t>
         </is>
       </c>
       <c r="AX444" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Mira Karlin Bittár</t>
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
       <c r="AZ444" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60535102</t>
+          <t>https://artportalen.se/Sighting/135359375</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>67887174</v>
+        <v>60535102</v>
       </c>
       <c r="B445" t="n">
-        <v>89079</v>
+        <v>57947</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52250,36 +52239,45 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>239209</v>
+        <v>102977</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P445" t="inlineStr">
         <is>
-          <t>Ornöboda, Ornö, Srm</t>
+          <t>Roffe Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>699293</v>
+        <v>699391</v>
       </c>
       <c r="R445" t="n">
-        <v>6557679</v>
+        <v>6557647</v>
       </c>
       <c r="S445" t="n">
         <v>50</v>
@@ -52306,17 +52304,22 @@
       </c>
       <c r="Y445" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA445" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
-        </is>
-      </c>
-      <c r="AC445" t="inlineStr">
-        <is>
-          <t>Exkursion med Stockholms Svampvänner.</t>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="AB445" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD445" t="b">
@@ -52325,34 +52328,33 @@
       <c r="AE445" t="b">
         <v>0</v>
       </c>
-      <c r="AF445" t="inlineStr"/>
       <c r="AG445" t="b">
         <v>0</v>
       </c>
       <c r="AT445" t="inlineStr"/>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
       <c r="AZ445" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67887174</t>
+          <t>https://artportalen.se/Sighting/60535102</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>67977656</v>
+        <v>67887174</v>
       </c>
       <c r="B446" t="n">
-        <v>75300</v>
+        <v>89079</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52360,21 +52362,21 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6428</v>
+        <v>239209</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I446" t="inlineStr"/>
@@ -52382,17 +52384,17 @@
       <c r="K446" t="inlineStr"/>
       <c r="P446" t="inlineStr">
         <is>
-          <t>Ornöboda, Srm</t>
+          <t>Ornöboda, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>699295</v>
+        <v>699293</v>
       </c>
       <c r="R446" t="n">
-        <v>6558099</v>
+        <v>6557679</v>
       </c>
       <c r="S446" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T446" t="inlineStr">
         <is>
@@ -52426,7 +52428,7 @@
       </c>
       <c r="AC446" t="inlineStr">
         <is>
-          <t>På gammal al.</t>
+          <t>Exkursion med Stockholms Svampvänner.</t>
         </is>
       </c>
       <c r="AD446" t="b">
@@ -52435,33 +52437,34 @@
       <c r="AE446" t="b">
         <v>0</v>
       </c>
+      <c r="AF446" t="inlineStr"/>
       <c r="AG446" t="b">
         <v>0</v>
       </c>
       <c r="AT446" t="inlineStr"/>
       <c r="AW446" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AX446" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
       <c r="AZ446" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67977656</t>
+          <t>https://artportalen.se/Sighting/67887174</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>61833368</v>
+        <v>67977656</v>
       </c>
       <c r="B447" t="n">
-        <v>4775</v>
+        <v>75300</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52469,37 +52472,39 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>100299</v>
+        <v>6428</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr"/>
       <c r="P447" t="inlineStr">
         <is>
-          <t>Ornöboda, Svinåker 3:40, Srm</t>
+          <t>Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>699294</v>
+        <v>699295</v>
       </c>
       <c r="R447" t="n">
-        <v>6558102</v>
+        <v>6558099</v>
       </c>
       <c r="S447" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="T447" t="inlineStr">
         <is>
@@ -52523,17 +52528,17 @@
       </c>
       <c r="Y447" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA447" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AC447" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>På gammal al.</t>
         </is>
       </c>
       <c r="AD447" t="b">
@@ -52548,31 +52553,27 @@
       <c r="AT447" t="inlineStr"/>
       <c r="AW447" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX447" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY447" t="inlineStr">
-        <is>
-          <t>Skötselplan Ornöboda Svinåker 3:15</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY447" t="inlineStr"/>
       <c r="AZ447" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61833368</t>
+          <t>https://artportalen.se/Sighting/67977656</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>60530282</v>
+        <v>61833368</v>
       </c>
       <c r="B448" t="n">
-        <v>58439</v>
+        <v>4775</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52580,48 +52581,37 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>103018</v>
+        <v>100299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I448" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K448" t="inlineStr"/>
-      <c r="L448" t="inlineStr"/>
-      <c r="M448" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr"/>
       <c r="P448" t="inlineStr">
         <is>
-          <t>Ornö, Ornöboda, Srm</t>
+          <t>Ornöboda, Svinåker 3:40, Srm</t>
         </is>
       </c>
       <c r="Q448" t="n">
-        <v>699373</v>
+        <v>699294</v>
       </c>
       <c r="R448" t="n">
-        <v>6557918</v>
+        <v>6558102</v>
       </c>
       <c r="S448" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -52645,22 +52635,17 @@
       </c>
       <c r="Y448" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="Z448" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AA448" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="AB448" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AC448" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AD448" t="b">
@@ -52675,77 +52660,80 @@
       <c r="AT448" t="inlineStr"/>
       <c r="AW448" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AX448" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
-        </is>
-      </c>
-      <c r="AY448" t="inlineStr"/>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY448" t="inlineStr">
+        <is>
+          <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
       <c r="AZ448" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60530282</t>
+          <t>https://artportalen.se/Sighting/61833368</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>118137472</v>
+        <v>60530282</v>
       </c>
       <c r="B449" t="n">
-        <v>57572</v>
+        <v>58439</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>205660</v>
+        <v>103018</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N449" t="inlineStr"/>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="P449" t="inlineStr">
         <is>
-          <t>Inloppet till Toren, Ornö, Srm</t>
+          <t>Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q449" t="n">
-        <v>699420</v>
+        <v>699373</v>
       </c>
       <c r="R449" t="n">
-        <v>6557948</v>
+        <v>6557918</v>
       </c>
       <c r="S449" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
@@ -52769,12 +52757,22 @@
       </c>
       <c r="Y449" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="Z449" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA449" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="AB449" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD449" t="b">
@@ -52789,65 +52787,77 @@
       <c r="AT449" t="inlineStr"/>
       <c r="AW449" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
       <c r="AZ449" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118137472</t>
+          <t>https://artportalen.se/Sighting/60530282</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>61833348</v>
+        <v>118137472</v>
       </c>
       <c r="B450" t="n">
-        <v>4781</v>
+        <v>57572</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>102306</v>
+        <v>205660</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I450" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr"/>
       <c r="P450" t="inlineStr">
         <is>
-          <t>Ornöboda, Svinåker 3:20, Srm</t>
+          <t>Inloppet till Toren, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>699344</v>
+        <v>699420</v>
       </c>
       <c r="R450" t="n">
-        <v>6558123</v>
+        <v>6557948</v>
       </c>
       <c r="S450" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T450" t="inlineStr">
         <is>
@@ -52871,17 +52881,12 @@
       </c>
       <c r="Y450" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA450" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AC450" t="inlineStr">
-        <is>
-          <t>Märkta av svs för fällning. Inväxta i ek.</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD450" t="b">
@@ -52896,20 +52901,127 @@
       <c r="AT450" t="inlineStr"/>
       <c r="AW450" t="inlineStr">
         <is>
+          <t>Per Åsberg</t>
+        </is>
+      </c>
+      <c r="AX450" t="inlineStr">
+        <is>
+          <t>Per Åsberg</t>
+        </is>
+      </c>
+      <c r="AY450" t="inlineStr"/>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118137472</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>61833348</v>
+      </c>
+      <c r="B451" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr"/>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>Ornöboda, Svinåker 3:20, Srm</t>
+        </is>
+      </c>
+      <c r="Q451" t="n">
+        <v>699344</v>
+      </c>
+      <c r="R451" t="n">
+        <v>6558123</v>
+      </c>
+      <c r="S451" t="n">
+        <v>15</v>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W451" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y451" t="inlineStr">
+        <is>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AA451" t="inlineStr">
+        <is>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AC451" t="inlineStr">
+        <is>
+          <t>Märkta av svs för fällning. Inväxta i ek.</t>
+        </is>
+      </c>
+      <c r="AD451" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE451" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG451" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT451" t="inlineStr"/>
+      <c r="AW451" t="inlineStr">
+        <is>
           <t>Anna Koffman</t>
         </is>
       </c>
-      <c r="AX450" t="inlineStr">
+      <c r="AX451" t="inlineStr">
         <is>
           <t>Anna Koffman</t>
         </is>
       </c>
-      <c r="AY450" t="inlineStr">
+      <c r="AY451" t="inlineStr">
         <is>
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
-      <c r="AZ450" t="inlineStr">
+      <c r="AZ451" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/61833348</t>
         </is>
@@ -53366,6 +53478,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ451"/>
+  <dimension ref="A1:AZ450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52116,48 +52116,59 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>135359375</v>
+        <v>60535102</v>
       </c>
       <c r="B444" t="n">
-        <v>56915</v>
+        <v>57947</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>100041</v>
+        <v>102977</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Coronella austriaca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Laurenti, 1768</t>
-        </is>
-      </c>
-      <c r="I444" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P444" t="inlineStr">
         <is>
-          <t>Brännkrok, Srm</t>
+          <t>Roffe Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q444" t="n">
-        <v>699406</v>
+        <v>699391</v>
       </c>
       <c r="R444" t="n">
-        <v>6557753</v>
+        <v>6557647</v>
       </c>
       <c r="S444" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -52181,22 +52192,22 @@
       </c>
       <c r="Y444" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="Z444" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA444" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="AB444" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD444" t="b">
@@ -52211,27 +52222,27 @@
       <c r="AT444" t="inlineStr"/>
       <c r="AW444" t="inlineStr">
         <is>
-          <t>Mira Karlin Bittár</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX444" t="inlineStr">
         <is>
-          <t>Mira Karlin Bittár</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
       <c r="AZ444" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135359375</t>
+          <t>https://artportalen.se/Sighting/60535102</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>60535102</v>
+        <v>67887174</v>
       </c>
       <c r="B445" t="n">
-        <v>57947</v>
+        <v>89079</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52239,45 +52250,36 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>102977</v>
+        <v>239209</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I445" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr"/>
-      <c r="L445" t="inlineStr"/>
-      <c r="M445" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P445" t="inlineStr">
         <is>
-          <t>Roffe Ornö, Ornöboda, Srm</t>
+          <t>Ornöboda, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>699391</v>
+        <v>699293</v>
       </c>
       <c r="R445" t="n">
-        <v>6557647</v>
+        <v>6557679</v>
       </c>
       <c r="S445" t="n">
         <v>50</v>
@@ -52304,22 +52306,17 @@
       </c>
       <c r="Y445" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
-        </is>
-      </c>
-      <c r="Z445" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA445" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
-        </is>
-      </c>
-      <c r="AB445" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2017-09-30</t>
+        </is>
+      </c>
+      <c r="AC445" t="inlineStr">
+        <is>
+          <t>Exkursion med Stockholms Svampvänner.</t>
         </is>
       </c>
       <c r="AD445" t="b">
@@ -52328,33 +52325,34 @@
       <c r="AE445" t="b">
         <v>0</v>
       </c>
+      <c r="AF445" t="inlineStr"/>
       <c r="AG445" t="b">
         <v>0</v>
       </c>
       <c r="AT445" t="inlineStr"/>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
       <c r="AZ445" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60535102</t>
+          <t>https://artportalen.se/Sighting/67887174</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>67887174</v>
+        <v>67977656</v>
       </c>
       <c r="B446" t="n">
-        <v>89079</v>
+        <v>75300</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52362,21 +52360,21 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>239209</v>
+        <v>6428</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I446" t="inlineStr"/>
@@ -52384,17 +52382,17 @@
       <c r="K446" t="inlineStr"/>
       <c r="P446" t="inlineStr">
         <is>
-          <t>Ornöboda, Ornö, Srm</t>
+          <t>Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>699293</v>
+        <v>699295</v>
       </c>
       <c r="R446" t="n">
-        <v>6557679</v>
+        <v>6558099</v>
       </c>
       <c r="S446" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T446" t="inlineStr">
         <is>
@@ -52428,7 +52426,7 @@
       </c>
       <c r="AC446" t="inlineStr">
         <is>
-          <t>Exkursion med Stockholms Svampvänner.</t>
+          <t>På gammal al.</t>
         </is>
       </c>
       <c r="AD446" t="b">
@@ -52437,34 +52435,33 @@
       <c r="AE446" t="b">
         <v>0</v>
       </c>
-      <c r="AF446" t="inlineStr"/>
       <c r="AG446" t="b">
         <v>0</v>
       </c>
       <c r="AT446" t="inlineStr"/>
       <c r="AW446" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX446" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
       <c r="AZ446" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67887174</t>
+          <t>https://artportalen.se/Sighting/67977656</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>67977656</v>
+        <v>61833368</v>
       </c>
       <c r="B447" t="n">
-        <v>75300</v>
+        <v>4775</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52472,39 +52469,37 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>6428</v>
+        <v>100299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I447" t="inlineStr"/>
-      <c r="J447" t="inlineStr"/>
-      <c r="K447" t="inlineStr"/>
       <c r="P447" t="inlineStr">
         <is>
-          <t>Ornöboda, Srm</t>
+          <t>Ornöboda, Svinåker 3:40, Srm</t>
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>699295</v>
+        <v>699294</v>
       </c>
       <c r="R447" t="n">
-        <v>6558099</v>
+        <v>6558102</v>
       </c>
       <c r="S447" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="T447" t="inlineStr">
         <is>
@@ -52528,17 +52523,17 @@
       </c>
       <c r="Y447" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AA447" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AC447" t="inlineStr">
         <is>
-          <t>På gammal al.</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AD447" t="b">
@@ -52553,27 +52548,31 @@
       <c r="AT447" t="inlineStr"/>
       <c r="AW447" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AX447" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY447" t="inlineStr"/>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY447" t="inlineStr">
+        <is>
+          <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
       <c r="AZ447" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67977656</t>
+          <t>https://artportalen.se/Sighting/61833368</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>61833368</v>
+        <v>60530282</v>
       </c>
       <c r="B448" t="n">
-        <v>4775</v>
+        <v>58439</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52581,37 +52580,48 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>100299</v>
+        <v>103018</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I448" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="P448" t="inlineStr">
         <is>
-          <t>Ornöboda, Svinåker 3:40, Srm</t>
+          <t>Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q448" t="n">
-        <v>699294</v>
+        <v>699373</v>
       </c>
       <c r="R448" t="n">
-        <v>6558102</v>
+        <v>6557918</v>
       </c>
       <c r="S448" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -52635,17 +52645,22 @@
       </c>
       <c r="Y448" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="Z448" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA448" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AC448" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="AB448" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD448" t="b">
@@ -52660,80 +52675,77 @@
       <c r="AT448" t="inlineStr"/>
       <c r="AW448" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX448" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY448" t="inlineStr">
-        <is>
-          <t>Skötselplan Ornöboda Svinåker 3:15</t>
-        </is>
-      </c>
+          <t>Henning Edgren</t>
+        </is>
+      </c>
+      <c r="AY448" t="inlineStr"/>
       <c r="AZ448" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61833368</t>
+          <t>https://artportalen.se/Sighting/60530282</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>60530282</v>
+        <v>118137472</v>
       </c>
       <c r="B449" t="n">
-        <v>58439</v>
+        <v>57572</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>103018</v>
+        <v>205660</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr"/>
       <c r="P449" t="inlineStr">
         <is>
-          <t>Ornö, Ornöboda, Srm</t>
+          <t>Inloppet till Toren, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q449" t="n">
-        <v>699373</v>
+        <v>699420</v>
       </c>
       <c r="R449" t="n">
-        <v>6557918</v>
+        <v>6557948</v>
       </c>
       <c r="S449" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
@@ -52757,22 +52769,12 @@
       </c>
       <c r="Y449" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="Z449" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA449" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="AB449" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD449" t="b">
@@ -52787,77 +52789,65 @@
       <c r="AT449" t="inlineStr"/>
       <c r="AW449" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Per Åsberg</t>
         </is>
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Per Åsberg</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
       <c r="AZ449" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60530282</t>
+          <t>https://artportalen.se/Sighting/118137472</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>118137472</v>
+        <v>61833348</v>
       </c>
       <c r="B450" t="n">
-        <v>57572</v>
+        <v>4781</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>205660</v>
+        <v>102306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K450" t="inlineStr"/>
-      <c r="L450" t="inlineStr"/>
-      <c r="M450" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N450" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr"/>
       <c r="P450" t="inlineStr">
         <is>
-          <t>Inloppet till Toren, Ornö, Srm</t>
+          <t>Ornöboda, Svinåker 3:20, Srm</t>
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>699420</v>
+        <v>699344</v>
       </c>
       <c r="R450" t="n">
-        <v>6557948</v>
+        <v>6558123</v>
       </c>
       <c r="S450" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T450" t="inlineStr">
         <is>
@@ -52881,12 +52871,17 @@
       </c>
       <c r="Y450" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AA450" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AC450" t="inlineStr">
+        <is>
+          <t>Märkta av svs för fällning. Inväxta i ek.</t>
         </is>
       </c>
       <c r="AD450" t="b">
@@ -52901,127 +52896,20 @@
       <c r="AT450" t="inlineStr"/>
       <c r="AW450" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AX450" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
-        </is>
-      </c>
-      <c r="AY450" t="inlineStr"/>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY450" t="inlineStr">
+        <is>
+          <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
       <c r="AZ450" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/118137472</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="n">
-        <v>61833348</v>
-      </c>
-      <c r="B451" t="n">
-        <v>4781</v>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E451" t="n">
-        <v>102306</v>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>Granbarkgnagare</t>
-        </is>
-      </c>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>Microbregma emarginatum</t>
-        </is>
-      </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I451" t="inlineStr"/>
-      <c r="P451" t="inlineStr">
-        <is>
-          <t>Ornöboda, Svinåker 3:20, Srm</t>
-        </is>
-      </c>
-      <c r="Q451" t="n">
-        <v>699344</v>
-      </c>
-      <c r="R451" t="n">
-        <v>6558123</v>
-      </c>
-      <c r="S451" t="n">
-        <v>15</v>
-      </c>
-      <c r="T451" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U451" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V451" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W451" t="inlineStr">
-        <is>
-          <t>Ornö</t>
-        </is>
-      </c>
-      <c r="Y451" t="inlineStr">
-        <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AA451" t="inlineStr">
-        <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AC451" t="inlineStr">
-        <is>
-          <t>Märkta av svs för fällning. Inväxta i ek.</t>
-        </is>
-      </c>
-      <c r="AD451" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE451" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG451" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT451" t="inlineStr"/>
-      <c r="AW451" t="inlineStr">
-        <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AX451" t="inlineStr">
-        <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY451" t="inlineStr">
-        <is>
-          <t>Skötselplan Ornöboda Svinåker 3:15</t>
-        </is>
-      </c>
-      <c r="AZ451" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/61833348</t>
         </is>
@@ -53478,7 +53366,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ450"/>
+  <dimension ref="A1:AZ451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52116,59 +52116,48 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>60535102</v>
+        <v>135359375</v>
       </c>
       <c r="B444" t="n">
-        <v>57947</v>
+        <v>56916</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>102977</v>
+        <v>100041</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I444" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K444" t="inlineStr"/>
-      <c r="L444" t="inlineStr"/>
-      <c r="M444" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Laurenti, 1768</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr"/>
       <c r="P444" t="inlineStr">
         <is>
-          <t>Roffe Ornö, Ornöboda, Srm</t>
+          <t>Brännkrok, Srm</t>
         </is>
       </c>
       <c r="Q444" t="n">
-        <v>699391</v>
+        <v>699406</v>
       </c>
       <c r="R444" t="n">
-        <v>6557647</v>
+        <v>6557753</v>
       </c>
       <c r="S444" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -52192,22 +52181,22 @@
       </c>
       <c r="Y444" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z444" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA444" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB444" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD444" t="b">
@@ -52222,27 +52211,27 @@
       <c r="AT444" t="inlineStr"/>
       <c r="AW444" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Mira Karlin Bittár</t>
         </is>
       </c>
       <c r="AX444" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Mira Karlin Bittár</t>
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
       <c r="AZ444" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60535102</t>
+          <t>https://artportalen.se/Sighting/135359375</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>67887174</v>
+        <v>60535102</v>
       </c>
       <c r="B445" t="n">
-        <v>89079</v>
+        <v>57947</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52250,36 +52239,45 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>239209</v>
+        <v>102977</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P445" t="inlineStr">
         <is>
-          <t>Ornöboda, Ornö, Srm</t>
+          <t>Roffe Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>699293</v>
+        <v>699391</v>
       </c>
       <c r="R445" t="n">
-        <v>6557679</v>
+        <v>6557647</v>
       </c>
       <c r="S445" t="n">
         <v>50</v>
@@ -52306,17 +52304,22 @@
       </c>
       <c r="Y445" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA445" t="inlineStr">
         <is>
-          <t>2017-09-30</t>
-        </is>
-      </c>
-      <c r="AC445" t="inlineStr">
-        <is>
-          <t>Exkursion med Stockholms Svampvänner.</t>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="AB445" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD445" t="b">
@@ -52325,34 +52328,33 @@
       <c r="AE445" t="b">
         <v>0</v>
       </c>
-      <c r="AF445" t="inlineStr"/>
       <c r="AG445" t="b">
         <v>0</v>
       </c>
       <c r="AT445" t="inlineStr"/>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
       <c r="AZ445" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67887174</t>
+          <t>https://artportalen.se/Sighting/60535102</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>67977656</v>
+        <v>67887174</v>
       </c>
       <c r="B446" t="n">
-        <v>75300</v>
+        <v>89079</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52360,21 +52362,21 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6428</v>
+        <v>239209</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I446" t="inlineStr"/>
@@ -52382,17 +52384,17 @@
       <c r="K446" t="inlineStr"/>
       <c r="P446" t="inlineStr">
         <is>
-          <t>Ornöboda, Srm</t>
+          <t>Ornöboda, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>699295</v>
+        <v>699293</v>
       </c>
       <c r="R446" t="n">
-        <v>6558099</v>
+        <v>6557679</v>
       </c>
       <c r="S446" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T446" t="inlineStr">
         <is>
@@ -52426,7 +52428,7 @@
       </c>
       <c r="AC446" t="inlineStr">
         <is>
-          <t>På gammal al.</t>
+          <t>Exkursion med Stockholms Svampvänner.</t>
         </is>
       </c>
       <c r="AD446" t="b">
@@ -52435,33 +52437,34 @@
       <c r="AE446" t="b">
         <v>0</v>
       </c>
+      <c r="AF446" t="inlineStr"/>
       <c r="AG446" t="b">
         <v>0</v>
       </c>
       <c r="AT446" t="inlineStr"/>
       <c r="AW446" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AX446" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
       <c r="AZ446" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67977656</t>
+          <t>https://artportalen.se/Sighting/67887174</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>61833368</v>
+        <v>67977656</v>
       </c>
       <c r="B447" t="n">
-        <v>4775</v>
+        <v>75300</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52469,37 +52472,39 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>100299</v>
+        <v>6428</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr"/>
       <c r="P447" t="inlineStr">
         <is>
-          <t>Ornöboda, Svinåker 3:40, Srm</t>
+          <t>Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>699294</v>
+        <v>699295</v>
       </c>
       <c r="R447" t="n">
-        <v>6558102</v>
+        <v>6558099</v>
       </c>
       <c r="S447" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="T447" t="inlineStr">
         <is>
@@ -52523,17 +52528,17 @@
       </c>
       <c r="Y447" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AA447" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2017-09-30</t>
         </is>
       </c>
       <c r="AC447" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>På gammal al.</t>
         </is>
       </c>
       <c r="AD447" t="b">
@@ -52548,31 +52553,27 @@
       <c r="AT447" t="inlineStr"/>
       <c r="AW447" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX447" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY447" t="inlineStr">
-        <is>
-          <t>Skötselplan Ornöboda Svinåker 3:15</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY447" t="inlineStr"/>
       <c r="AZ447" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61833368</t>
+          <t>https://artportalen.se/Sighting/67977656</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>60530282</v>
+        <v>61833368</v>
       </c>
       <c r="B448" t="n">
-        <v>58439</v>
+        <v>4775</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52580,48 +52581,37 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>103018</v>
+        <v>100299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I448" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K448" t="inlineStr"/>
-      <c r="L448" t="inlineStr"/>
-      <c r="M448" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr"/>
       <c r="P448" t="inlineStr">
         <is>
-          <t>Ornö, Ornöboda, Srm</t>
+          <t>Ornöboda, Svinåker 3:40, Srm</t>
         </is>
       </c>
       <c r="Q448" t="n">
-        <v>699373</v>
+        <v>699294</v>
       </c>
       <c r="R448" t="n">
-        <v>6557918</v>
+        <v>6558102</v>
       </c>
       <c r="S448" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -52645,22 +52635,17 @@
       </c>
       <c r="Y448" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="Z448" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2015-10-28</t>
         </is>
       </c>
       <c r="AA448" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
-        </is>
-      </c>
-      <c r="AB448" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AC448" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AD448" t="b">
@@ -52675,77 +52660,80 @@
       <c r="AT448" t="inlineStr"/>
       <c r="AW448" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AX448" t="inlineStr">
         <is>
-          <t>Henning Edgren</t>
-        </is>
-      </c>
-      <c r="AY448" t="inlineStr"/>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY448" t="inlineStr">
+        <is>
+          <t>Skötselplan Ornöboda Svinåker 3:15</t>
+        </is>
+      </c>
       <c r="AZ448" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60530282</t>
+          <t>https://artportalen.se/Sighting/61833368</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>118137472</v>
+        <v>60530282</v>
       </c>
       <c r="B449" t="n">
-        <v>57572</v>
+        <v>58439</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>205660</v>
+        <v>103018</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N449" t="inlineStr"/>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="P449" t="inlineStr">
         <is>
-          <t>Inloppet till Toren, Ornö, Srm</t>
+          <t>Ornö, Ornöboda, Srm</t>
         </is>
       </c>
       <c r="Q449" t="n">
-        <v>699420</v>
+        <v>699373</v>
       </c>
       <c r="R449" t="n">
-        <v>6557948</v>
+        <v>6557918</v>
       </c>
       <c r="S449" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
@@ -52769,12 +52757,22 @@
       </c>
       <c r="Y449" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="Z449" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA449" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2016-07-12</t>
+        </is>
+      </c>
+      <c r="AB449" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD449" t="b">
@@ -52789,65 +52787,77 @@
       <c r="AT449" t="inlineStr"/>
       <c r="AW449" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Henning Edgren</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
       <c r="AZ449" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118137472</t>
+          <t>https://artportalen.se/Sighting/60530282</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>61833348</v>
+        <v>118137472</v>
       </c>
       <c r="B450" t="n">
-        <v>4781</v>
+        <v>57572</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>102306</v>
+        <v>205660</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I450" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr"/>
       <c r="P450" t="inlineStr">
         <is>
-          <t>Ornöboda, Svinåker 3:20, Srm</t>
+          <t>Inloppet till Toren, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>699344</v>
+        <v>699420</v>
       </c>
       <c r="R450" t="n">
-        <v>6558123</v>
+        <v>6557948</v>
       </c>
       <c r="S450" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T450" t="inlineStr">
         <is>
@@ -52871,17 +52881,12 @@
       </c>
       <c r="Y450" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA450" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
-        </is>
-      </c>
-      <c r="AC450" t="inlineStr">
-        <is>
-          <t>Märkta av svs för fällning. Inväxta i ek.</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD450" t="b">
@@ -52896,20 +52901,127 @@
       <c r="AT450" t="inlineStr"/>
       <c r="AW450" t="inlineStr">
         <is>
+          <t>Per Åsberg</t>
+        </is>
+      </c>
+      <c r="AX450" t="inlineStr">
+        <is>
+          <t>Per Åsberg</t>
+        </is>
+      </c>
+      <c r="AY450" t="inlineStr"/>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118137472</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>61833348</v>
+      </c>
+      <c r="B451" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr"/>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>Ornöboda, Svinåker 3:20, Srm</t>
+        </is>
+      </c>
+      <c r="Q451" t="n">
+        <v>699344</v>
+      </c>
+      <c r="R451" t="n">
+        <v>6558123</v>
+      </c>
+      <c r="S451" t="n">
+        <v>15</v>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W451" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y451" t="inlineStr">
+        <is>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AA451" t="inlineStr">
+        <is>
+          <t>2015-10-28</t>
+        </is>
+      </c>
+      <c r="AC451" t="inlineStr">
+        <is>
+          <t>Märkta av svs för fällning. Inväxta i ek.</t>
+        </is>
+      </c>
+      <c r="AD451" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE451" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG451" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT451" t="inlineStr"/>
+      <c r="AW451" t="inlineStr">
+        <is>
           <t>Anna Koffman</t>
         </is>
       </c>
-      <c r="AX450" t="inlineStr">
+      <c r="AX451" t="inlineStr">
         <is>
           <t>Anna Koffman</t>
         </is>
       </c>
-      <c r="AY450" t="inlineStr">
+      <c r="AY451" t="inlineStr">
         <is>
           <t>Skötselplan Ornöboda Svinåker 3:15</t>
         </is>
       </c>
-      <c r="AZ450" t="inlineStr">
+      <c r="AZ451" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/61833348</t>
         </is>
@@ -53366,6 +53478,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -52119,7 +52119,7 @@
         <v>135359375</v>
       </c>
       <c r="B444" t="n">
-        <v>56916</v>
+        <v>56920</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -52119,7 +52119,7 @@
         <v>135359375</v>
       </c>
       <c r="B444" t="n">
-        <v>56920</v>
+        <v>56921</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
